--- a/docs/scope-relevance-TO-FILL.xlsx
+++ b/docs/scope-relevance-TO-FILL.xlsx
@@ -7,6 +7,7 @@
     <sheet name="1. Relevance" sheetId="2" r:id="rId2"/>
     <sheet name="2. Today" sheetId="3" r:id="rId3"/>
     <sheet name="3. Where the tiles are" sheetId="4" r:id="rId4"/>
+    <sheet name="4. Level of works" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -401,206 +402,296 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C47"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="62.83203125" customWidth="1"/>
     <col min="3" max="3" width="58.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Scope relevance — which elements each project type offers by default</v>
+        <v>Scope relevance — which elements each project type offers, and how each one is priced</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Generated 2026-09-21 by scripts/build-scope-relevance-sheet.mjs</v>
+        <v>Generated 2026-09-22 by scripts/build-scope-relevance-sheet.mjs</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>The problem this solves</v>
+        <v>What this sheet decides — and what it does NOT</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Q2.2 shows up to 98 tiles on a new build. Three NRM1 groups carry 76 of them: group 4 (fittings, 35 tiles), group 5 (M&amp;E, 28) and group 8 (external works, 13).</v>
+        <v>It decides what reaches the Q2.3 tick-list. It does NOT decide price.</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Once this sheet is filled, the picker shows the Core elements and folds everything Optional behind a "+N more" disclosure per group. Nothing is ever unreachable.</v>
+        <v>Price comes only from what the user actually ticks in Q2.3, and the specification level in Q2.4.</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>What to do</v>
+        <v>The problem this solves</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1.</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Open sheet "1. Relevance". Columns H to N are one per project type and are ALREADY FILLED with a suggestion.</v>
+        <v>Q2.3 shows up to 98 tiles on a new build. Three NRM1 groups carry 76 of them: group 4 (fittings, 35 tiles), group 5 (M&amp;E, 34) and group 8 (external works, 13).</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2.</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Correct the ones that are wrong. You are editing, not authoring — most rows will be right.</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>3.</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Only three values are valid. Anything else is treated as Optional.</v>
+        <v>Once this sheet is filled, the picker shows the Core elements and folds everything Optional behind a "+N more" disclosure per group. Nothing is ever unreachable.</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>What to do</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Value</v>
+        <v>1.</v>
       </c>
       <c r="B13" t="str">
-        <v>Meaning</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Effect on the picker</v>
+        <v>Open sheet "1. Relevance". The project-type columns are ALREADY FILLED with a suggestion.</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Core</v>
+        <v>2.</v>
       </c>
       <c r="B14" t="str">
-        <v>A project of this type usually includes this element</v>
-      </c>
-      <c r="C14" t="str">
-        <v>Shown by default, in its group</v>
+        <v>Correct the ones that are wrong. You are editing, not authoring — most rows will be right.</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Optional</v>
+        <v>3.</v>
       </c>
       <c r="B15" t="str">
-        <v>Sometimes relevant — the user should be able to find it</v>
-      </c>
-      <c r="C15" t="str">
-        <v>Folded behind "+N more" in its group</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Cannot apply, or has no rate for this type</v>
-      </c>
-      <c r="C16" t="str">
-        <v>Not offered at all</v>
+        <v>Only three values are valid. Anything else is treated as Optional.</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Value</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Meaning</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Effect on the picker</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Where the suggestion came from</v>
+        <v>Core</v>
+      </c>
+      <c r="B18" t="str">
+        <v>A project of this type usually includes this element</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Shown by default, in its group</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="B19" t="str">
-        <v>Derived: the element has no rate in that type’s rate family, or its NRM1 group is not offered for that type. These are facts, not opinions — change one only if you intend to add a rate.</v>
+        <v>Sometimes relevant — the user should be able to find it</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Folded behind "+N more" in its group</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Core</v>
+        <v>N/A</v>
       </c>
       <c r="B20" t="str">
-        <v>Derived: the element is in that type’s existing "Use typical scope" preset. That preset is deliberately conservative, so expect to promote things — external works especially, where it only picks site preparation.</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>Optional</v>
-      </c>
-      <c r="B21" t="str">
-        <v>Everything else that is priceable and visible today.</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>The intervention-level dimension</v>
+        <v>Cannot apply, or has no rate for this type</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Not offered at all</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Core is NOT pre-ticked. It only decides where the tile sits on the page. Nothing reaches the price except by the user ticking it.</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Column F "Min Lvl" is the workbook’s own value: the lowest Q2.3 tier at which the element becomes selectable on a refurbishment-family project. 1 = fabric and finishes only, 4 = reconfiguration or full redesign.</v>
+        <v>Where the suggestion came from</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Column G is blank for you to override it. Leave blank to keep the workbook value.</v>
+        <v>N/A</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Derived: the element has no rate in that type’s rate family, or its NRM1 group is not offered for that type. These are facts, not opinions — change one only if you intend to add a rate.</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Core</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Derived: the element is in that type’s existing "Use typical scope" preset. That preset is deliberately conservative, so expect to promote things — external works especially, where it only picks site preparation.</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Specification level is deliberately NOT an axis here</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>Q2.4 picks which rate COLUMN is read for an element, not whether the element applies. If you think spec level should also narrow the list, say so and it becomes another set of columns.</v>
+        <v>Optional</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Everything else that is priceable and visible today.</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>The three columns that are yours to change</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Building use</v>
+        <v>Building use (override)</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Which Q1.3 building uses this element applies to. "All" means any. Leave blank to keep the workbook value.</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Column D shows the workbook’s Building Use tags, which already filter the picker independently. 62 of 112 rows are tagged "All", which is why that filter alone leaves so many tiles.</v>
+        <v/>
+      </c>
+      <c r="B31" t="str">
+        <v>Building use will DEMOTE a Core element to Optional when it does not match — it will never hide it. That is the fix for the bar counter being unreachable in a university coffee shop.</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Sheet "2. Today" shows how many tiles each combination currently produces, so you can see what the change is worth.</v>
+        <v>Min Lvl (override)</v>
+      </c>
+      <c r="B32" t="str">
+        <v>The lowest Q2.2 Level of Works at which this element becomes available. 1 = always available. Leave blank to keep the workbook value.</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v/>
+      </c>
+      <c r="B33" t="str">
+        <v>Min Lvl only applies to Refurbishment, Fit-out and Extension. New Build, External works only, Demolition only and Other or mixed ignore it entirely.</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Notes</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Anything you want recorded against the row. Carried forward when this sheet is regenerated.</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>The "Priced on" column is read-only, and is worth checking</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Charged across the whole building. Right for finishes, partitions, services, facade.</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>One floor (footprint)</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Charged on GIFA ÷ storeys. Right for roof, foundations, ground slab — you only have one of each.</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Upper floors only</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Charged on GIFA × (storeys − 1) ÷ storeys. Right for suspended upper floor structure.</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Per unit / Lump sum</v>
+      </c>
+      <c r="B40" t="str">
+        <v>A count or a single figure, not an area.</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>A wrong basis is as costly as a wrong relevance: 2.9 tanking was charged across every floor of the building when it only applies to one.</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Specification level is deliberately NOT an axis here</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Q2.4 picks which rate COLUMN is read for an element, not whether the element applies.</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Regenerating this sheet is safe</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Re-running the script carries every answer forward automatically. Fill it in as you go.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C32"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C47"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O113"/>
+  <dimension ref="A1:R113"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="7.83203125" customWidth="1"/>
-    <col min="3" max="3" width="58.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="17.83203125" customWidth="1"/>
-    <col min="7" max="7" width="17.83203125" customWidth="1"/>
-    <col min="8" max="8" width="15.83203125" customWidth="1"/>
-    <col min="9" max="9" width="15.83203125" customWidth="1"/>
-    <col min="10" max="10" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="52.83203125" customWidth="1"/>
+    <col min="4" max="4" width="22.83203125" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" customWidth="1"/>
+    <col min="6" max="6" width="40.83203125" customWidth="1"/>
+    <col min="7" max="7" width="26.83203125" customWidth="1"/>
+    <col min="8" max="8" width="26.83203125" customWidth="1"/>
+    <col min="9" max="9" width="30.83203125" customWidth="1"/>
+    <col min="10" max="10" width="18.83203125" customWidth="1"/>
     <col min="11" max="11" width="15.83203125" customWidth="1"/>
     <col min="12" max="12" width="15.83203125" customWidth="1"/>
     <col min="13" max="13" width="15.83203125" customWidth="1"/>
     <col min="14" max="14" width="15.83203125" customWidth="1"/>
-    <col min="15" max="15" width="40.83203125" customWidth="1"/>
+    <col min="15" max="15" width="15.83203125" customWidth="1"/>
+    <col min="16" max="16" width="15.83203125" customWidth="1"/>
+    <col min="17" max="17" width="15.83203125" customWidth="1"/>
+    <col min="18" max="18" width="40.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -614,39 +705,48 @@
         <v>Element / description</v>
       </c>
       <c r="D1" t="str">
-        <v>Building Use tags</v>
+        <v>Priced on</v>
       </c>
       <c r="E1" t="str">
-        <v>Pricing type</v>
+        <v>NRM1 Ref</v>
       </c>
       <c r="F1" t="str">
+        <v>NRM1 element</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Building Use (workbook)</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Building use (override)</v>
+      </c>
+      <c r="I1" t="str">
         <v>Min Lvl (workbook)</v>
       </c>
-      <c r="G1" t="str">
+      <c r="J1" t="str">
         <v>Min Lvl (override)</v>
       </c>
-      <c r="H1" t="str">
+      <c r="K1" t="str">
         <v>New Build</v>
       </c>
-      <c r="I1" t="str">
+      <c r="L1" t="str">
         <v>Extension</v>
       </c>
-      <c r="J1" t="str">
+      <c r="M1" t="str">
         <v>Refurbishment</v>
       </c>
-      <c r="K1" t="str">
+      <c r="N1" t="str">
         <v>Fit-out</v>
       </c>
-      <c r="L1" t="str">
+      <c r="O1" t="str">
         <v>External works only</v>
       </c>
-      <c r="M1" t="str">
+      <c r="P1" t="str">
         <v>Demolition only</v>
       </c>
-      <c r="N1" t="str">
+      <c r="Q1" t="str">
         <v>Other or mixed</v>
       </c>
-      <c r="O1" t="str">
+      <c r="R1" t="str">
         <v>Notes</v>
       </c>
     </row>
@@ -661,39 +761,48 @@
         <v>Toxic/hazardous material removal</v>
       </c>
       <c r="D2" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E2" t="str">
+        <v>0.1</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Toxic/hazardous material removal</v>
+      </c>
+      <c r="G2" t="str">
         <v>All</v>
       </c>
-      <c r="E2" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2" t="str">
-        <v/>
-      </c>
       <c r="H2" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>Optional</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J2" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K2" t="str">
         <v>N/A</v>
       </c>
       <c r="L2" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M2" t="str">
         <v>Optional</v>
       </c>
       <c r="N2" t="str">
-        <v>Optional</v>
+        <v>N/A</v>
       </c>
       <c r="O2" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P2" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R2" t="str">
         <v/>
       </c>
     </row>
@@ -708,25 +817,25 @@
         <v>Demolition &amp; structural alterations</v>
       </c>
       <c r="D3" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E3" t="str">
+        <v>0.2</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Major demolition works</v>
+      </c>
+      <c r="G3" t="str">
         <v>All</v>
       </c>
-      <c r="E3" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F3">
-        <v>4</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
       <c r="H3" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>Optional</v>
+        <v>4 Reconfiguration or full redesign</v>
       </c>
       <c r="J3" t="str">
-        <v>Core</v>
+        <v/>
       </c>
       <c r="K3" t="str">
         <v>N/A</v>
@@ -738,9 +847,18 @@
         <v>Core</v>
       </c>
       <c r="N3" t="str">
-        <v>Optional</v>
+        <v>N/A</v>
       </c>
       <c r="O3" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="P3" t="str">
+        <v>Core</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R3" t="str">
         <v/>
       </c>
     </row>
@@ -755,28 +873,28 @@
         <v>Contaminated land remediation</v>
       </c>
       <c r="D4" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E4" t="str">
+        <v>0.4</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Specialist groundworks</v>
+      </c>
+      <c r="G4" t="str">
         <v>All</v>
       </c>
-      <c r="E4" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F4">
-        <v>4</v>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
       <c r="H4" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>Optional</v>
+        <v>4 Reconfiguration or full redesign</v>
       </c>
       <c r="J4" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K4" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="L4" t="str">
         <v>Optional</v>
@@ -785,9 +903,18 @@
         <v>Optional</v>
       </c>
       <c r="N4" t="str">
-        <v>Optional</v>
+        <v>N/A</v>
       </c>
       <c r="O4" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="P4" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R4" t="str">
         <v/>
       </c>
     </row>
@@ -802,28 +929,28 @@
         <v>Ground stabilisation</v>
       </c>
       <c r="D5" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E5" t="str">
+        <v>0.4</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Specialist groundworks</v>
+      </c>
+      <c r="G5" t="str">
         <v>All</v>
       </c>
-      <c r="E5" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
       <c r="H5" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>Optional</v>
+        <v>4 Reconfiguration or full redesign</v>
       </c>
       <c r="J5" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="K5" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="L5" t="str">
         <v>Optional</v>
@@ -832,9 +959,18 @@
         <v>N/A</v>
       </c>
       <c r="N5" t="str">
-        <v>Optional</v>
+        <v>N/A</v>
       </c>
       <c r="O5" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="P5" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R5" t="str">
         <v/>
       </c>
     </row>
@@ -849,25 +985,25 @@
         <v>Soft strip of finishes &amp; fittings</v>
       </c>
       <c r="D6" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E6" t="str">
+        <v>7.1</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Minor demolition works and alterations</v>
+      </c>
+      <c r="G6" t="str">
         <v>All</v>
       </c>
-      <c r="E6" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
       <c r="H6" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>N/A</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J6" t="str">
-        <v>Core</v>
+        <v/>
       </c>
       <c r="K6" t="str">
         <v>N/A</v>
@@ -879,9 +1015,18 @@
         <v>Core</v>
       </c>
       <c r="N6" t="str">
-        <v>Optional</v>
+        <v>N/A</v>
       </c>
       <c r="O6" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P6" t="str">
+        <v>Core</v>
+      </c>
+      <c r="Q6" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R6" t="str">
         <v/>
       </c>
     </row>
@@ -896,39 +1041,48 @@
         <v>Standard foundations (strip/pad)</v>
       </c>
       <c r="D7" t="str">
+        <v>One floor (footprint)</v>
+      </c>
+      <c r="E7" t="str">
+        <v>1.1.1</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Substructure — standard foundations</v>
+      </c>
+      <c r="G7" t="str">
         <v>All</v>
       </c>
-      <c r="E7" t="str">
-        <v>footprint_rate</v>
-      </c>
-      <c r="F7">
-        <v>4</v>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
       <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>4 Reconfiguration or full redesign</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
         <v>Core</v>
       </c>
-      <c r="I7" t="str">
+      <c r="L7" t="str">
         <v>Core</v>
       </c>
-      <c r="J7" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="K7" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="L7" t="str">
-        <v>N/A</v>
-      </c>
       <c r="M7" t="str">
         <v>N/A</v>
       </c>
       <c r="N7" t="str">
-        <v>Optional</v>
+        <v>N/A</v>
       </c>
       <c r="O7" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P7" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q7" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R7" t="str">
         <v/>
       </c>
     </row>
@@ -943,39 +1097,48 @@
         <v>Specialist foundations (piled)</v>
       </c>
       <c r="D8" t="str">
+        <v>One floor (footprint)</v>
+      </c>
+      <c r="E8" t="str">
+        <v>1.1.2</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Substructure — specialist foundations</v>
+      </c>
+      <c r="G8" t="str">
         <v>All</v>
       </c>
-      <c r="E8" t="str">
-        <v>footprint_rate</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
       <c r="H8" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>Optional</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J8" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="K8" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="L8" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M8" t="str">
         <v>N/A</v>
       </c>
       <c r="N8" t="str">
-        <v>Optional</v>
+        <v>N/A</v>
       </c>
       <c r="O8" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P8" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q8" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R8" t="str">
         <v/>
       </c>
     </row>
@@ -990,39 +1153,48 @@
         <v>Lowest floor construction (slab)</v>
       </c>
       <c r="D9" t="str">
+        <v>One floor (footprint)</v>
+      </c>
+      <c r="E9" t="str">
+        <v>1.1.3</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Substructure — lowest floor construction</v>
+      </c>
+      <c r="G9" t="str">
         <v>All</v>
       </c>
-      <c r="E9" t="str">
-        <v>footprint_rate</v>
-      </c>
-      <c r="F9">
-        <v>4</v>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
       <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>4 Reconfiguration or full redesign</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
         <v>Core</v>
       </c>
-      <c r="I9" t="str">
+      <c r="L9" t="str">
         <v>Core</v>
       </c>
-      <c r="J9" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="K9" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="L9" t="str">
-        <v>N/A</v>
-      </c>
       <c r="M9" t="str">
         <v>N/A</v>
       </c>
       <c r="N9" t="str">
-        <v>Optional</v>
+        <v>N/A</v>
       </c>
       <c r="O9" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P9" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q9" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R9" t="str">
         <v/>
       </c>
     </row>
@@ -1037,39 +1209,48 @@
         <v>Basement excavation &amp; structure</v>
       </c>
       <c r="D10" t="str">
+        <v>One floor (footprint)</v>
+      </c>
+      <c r="E10" t="str">
+        <v>1.1.4</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Substructure — basement excavation</v>
+      </c>
+      <c r="G10" t="str">
         <v>All</v>
       </c>
-      <c r="E10" t="str">
-        <v>footprint_rate</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
       <c r="H10" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v>Optional</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J10" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="K10" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="L10" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M10" t="str">
         <v>N/A</v>
       </c>
       <c r="N10" t="str">
-        <v>Optional</v>
+        <v>N/A</v>
       </c>
       <c r="O10" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P10" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q10" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R10" t="str">
         <v/>
       </c>
     </row>
@@ -1084,39 +1265,48 @@
         <v>Structural frame</v>
       </c>
       <c r="D11" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E11" t="str">
+        <v>2.1</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Frame</v>
+      </c>
+      <c r="G11" t="str">
         <v>All</v>
       </c>
-      <c r="E11" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F11">
-        <v>4</v>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
       <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>4 Reconfiguration or full redesign</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
         <v>Core</v>
       </c>
-      <c r="I11" t="str">
+      <c r="L11" t="str">
         <v>Core</v>
       </c>
-      <c r="J11" t="str">
-        <v>Optional</v>
-      </c>
-      <c r="K11" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="L11" t="str">
-        <v>N/A</v>
-      </c>
       <c r="M11" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N11" t="str">
-        <v>Optional</v>
+        <v>N/A</v>
       </c>
       <c r="O11" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P11" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q11" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R11" t="str">
         <v/>
       </c>
     </row>
@@ -1131,39 +1321,48 @@
         <v>Upper floors</v>
       </c>
       <c r="D12" t="str">
+        <v>Upper floors only</v>
+      </c>
+      <c r="E12" t="str">
+        <v>2.2</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Upper floors</v>
+      </c>
+      <c r="G12" t="str">
         <v>All</v>
       </c>
-      <c r="E12" t="str">
-        <v>upperfloors_rate</v>
-      </c>
-      <c r="F12">
-        <v>4</v>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
       <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>4 Reconfiguration or full redesign</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
         <v>Core</v>
       </c>
-      <c r="I12" t="str">
+      <c r="L12" t="str">
         <v>Core</v>
       </c>
-      <c r="J12" t="str">
-        <v>Optional</v>
-      </c>
-      <c r="K12" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="L12" t="str">
-        <v>N/A</v>
-      </c>
       <c r="M12" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N12" t="str">
-        <v>Optional</v>
+        <v>N/A</v>
       </c>
       <c r="O12" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P12" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q12" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R12" t="str">
         <v/>
       </c>
     </row>
@@ -1178,39 +1377,48 @@
         <v>Roof structure &amp; covering</v>
       </c>
       <c r="D13" t="str">
+        <v>One floor (footprint)</v>
+      </c>
+      <c r="E13" t="str">
+        <v>2.3</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Roof</v>
+      </c>
+      <c r="G13" t="str">
         <v>All</v>
       </c>
-      <c r="E13" t="str">
-        <v>footprint_rate</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
       <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>1 Fabric and finishes only</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
         <v>Core</v>
       </c>
-      <c r="I13" t="str">
+      <c r="L13" t="str">
         <v>Core</v>
       </c>
-      <c r="J13" t="str">
-        <v>Optional</v>
-      </c>
-      <c r="K13" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="L13" t="str">
-        <v>N/A</v>
-      </c>
       <c r="M13" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N13" t="str">
-        <v>Optional</v>
+        <v>N/A</v>
       </c>
       <c r="O13" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P13" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q13" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R13" t="str">
         <v/>
       </c>
     </row>
@@ -1225,39 +1433,48 @@
         <v>Stairs &amp; ramps</v>
       </c>
       <c r="D14" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E14" t="str">
+        <v>2.4</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Stairs and ramps</v>
+      </c>
+      <c r="G14" t="str">
         <v>All</v>
       </c>
-      <c r="E14" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F14">
-        <v>2</v>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
       <c r="H14" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I14" t="str">
-        <v>Optional</v>
+        <v>2 Finishes with minor services</v>
       </c>
       <c r="J14" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K14" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="L14" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M14" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N14" t="str">
-        <v>Optional</v>
+        <v>N/A</v>
       </c>
       <c r="O14" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P14" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q14" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R14" t="str">
         <v/>
       </c>
     </row>
@@ -1272,39 +1489,48 @@
         <v>External walls &amp; facade</v>
       </c>
       <c r="D15" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E15" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="F15" t="str">
+        <v>External walls</v>
+      </c>
+      <c r="G15" t="str">
         <v>All</v>
       </c>
-      <c r="E15" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
       <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>1 Fabric and finishes only</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
         <v>Core</v>
       </c>
-      <c r="I15" t="str">
+      <c r="L15" t="str">
         <v>Core</v>
       </c>
-      <c r="J15" t="str">
-        <v>Optional</v>
-      </c>
-      <c r="K15" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="L15" t="str">
-        <v>N/A</v>
-      </c>
       <c r="M15" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N15" t="str">
-        <v>Optional</v>
+        <v>N/A</v>
       </c>
       <c r="O15" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P15" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q15" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R15" t="str">
         <v/>
       </c>
     </row>
@@ -1319,39 +1545,48 @@
         <v>Windows &amp; external doors</v>
       </c>
       <c r="D16" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E16" t="str">
+        <v>2.6</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Windows and external doors</v>
+      </c>
+      <c r="G16" t="str">
         <v>All</v>
       </c>
-      <c r="E16" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
       <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>1 Fabric and finishes only</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
         <v>Core</v>
       </c>
-      <c r="I16" t="str">
+      <c r="L16" t="str">
         <v>Core</v>
       </c>
-      <c r="J16" t="str">
-        <v>Optional</v>
-      </c>
-      <c r="K16" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="L16" t="str">
-        <v>N/A</v>
-      </c>
       <c r="M16" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N16" t="str">
-        <v>Optional</v>
+        <v>N/A</v>
       </c>
       <c r="O16" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P16" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q16" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R16" t="str">
         <v/>
       </c>
     </row>
@@ -1366,39 +1601,48 @@
         <v>Internal walls &amp; partitions</v>
       </c>
       <c r="D17" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E17" t="str">
+        <v>2.7</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Internal walls and partitions</v>
+      </c>
+      <c r="G17" t="str">
         <v>All</v>
       </c>
-      <c r="E17" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F17">
-        <v>4</v>
-      </c>
-      <c r="G17" t="str">
-        <v/>
-      </c>
       <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>4 Reconfiguration or full redesign</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
         <v>Core</v>
       </c>
-      <c r="I17" t="str">
+      <c r="L17" t="str">
         <v>Core</v>
       </c>
-      <c r="J17" t="str">
+      <c r="M17" t="str">
         <v>Core</v>
       </c>
-      <c r="K17" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="L17" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="M17" t="str">
-        <v>N/A</v>
-      </c>
       <c r="N17" t="str">
-        <v>Optional</v>
+        <v>N/A</v>
       </c>
       <c r="O17" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P17" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q17" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R17" t="str">
         <v/>
       </c>
     </row>
@@ -1413,39 +1657,48 @@
         <v>Internal doors &amp; ironmongery</v>
       </c>
       <c r="D18" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E18" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Internal doors</v>
+      </c>
+      <c r="G18" t="str">
         <v>All</v>
       </c>
-      <c r="E18" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-      <c r="G18" t="str">
-        <v/>
-      </c>
       <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>1 Fabric and finishes only</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
         <v>Core</v>
       </c>
-      <c r="I18" t="str">
+      <c r="L18" t="str">
         <v>Core</v>
       </c>
-      <c r="J18" t="str">
+      <c r="M18" t="str">
         <v>Core</v>
       </c>
-      <c r="K18" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="L18" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="M18" t="str">
-        <v>N/A</v>
-      </c>
       <c r="N18" t="str">
-        <v>Optional</v>
+        <v>N/A</v>
       </c>
       <c r="O18" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P18" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q18" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R18" t="str">
         <v/>
       </c>
     </row>
@@ -1460,39 +1713,48 @@
         <v>Waterproofing &amp; tanking</v>
       </c>
       <c r="D19" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E19" t="str">
+        <v>1.1.5</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Substructure — basement retaining walls</v>
+      </c>
+      <c r="G19" t="str">
         <v>All</v>
       </c>
-      <c r="E19" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19" t="str">
-        <v/>
-      </c>
       <c r="H19" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I19" t="str">
-        <v>Optional</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J19" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K19" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="L19" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M19" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N19" t="str">
-        <v>Optional</v>
+        <v>N/A</v>
       </c>
       <c r="O19" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P19" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q19" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R19" t="str">
         <v/>
       </c>
     </row>
@@ -1507,39 +1769,48 @@
         <v>Wall finishes</v>
       </c>
       <c r="D20" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E20" t="str">
+        <v>3.1</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Wall finishes</v>
+      </c>
+      <c r="G20" t="str">
         <v>All</v>
       </c>
-      <c r="E20" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-      <c r="G20" t="str">
-        <v/>
-      </c>
       <c r="H20" t="str">
-        <v>Core</v>
+        <v/>
       </c>
       <c r="I20" t="str">
-        <v>Core</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J20" t="str">
-        <v>Core</v>
+        <v/>
       </c>
       <c r="K20" t="str">
         <v>Core</v>
       </c>
       <c r="L20" t="str">
-        <v>N/A</v>
+        <v>Core</v>
       </c>
       <c r="M20" t="str">
-        <v>N/A</v>
+        <v>Core</v>
       </c>
       <c r="N20" t="str">
-        <v>Optional</v>
+        <v>Core</v>
       </c>
       <c r="O20" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P20" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q20" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R20" t="str">
         <v/>
       </c>
     </row>
@@ -1554,39 +1825,48 @@
         <v>Floor finishes</v>
       </c>
       <c r="D21" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E21" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Floor finishes</v>
+      </c>
+      <c r="G21" t="str">
         <v>All</v>
       </c>
-      <c r="E21" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-      <c r="G21" t="str">
-        <v/>
-      </c>
       <c r="H21" t="str">
-        <v>Core</v>
+        <v/>
       </c>
       <c r="I21" t="str">
-        <v>Core</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J21" t="str">
-        <v>Core</v>
+        <v/>
       </c>
       <c r="K21" t="str">
         <v>Core</v>
       </c>
       <c r="L21" t="str">
-        <v>N/A</v>
+        <v>Core</v>
       </c>
       <c r="M21" t="str">
-        <v>N/A</v>
+        <v>Core</v>
       </c>
       <c r="N21" t="str">
-        <v>Optional</v>
+        <v>Core</v>
       </c>
       <c r="O21" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P21" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q21" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R21" t="str">
         <v/>
       </c>
     </row>
@@ -1601,39 +1881,48 @@
         <v>Ceiling finishes</v>
       </c>
       <c r="D22" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E22" t="str">
+        <v>3.3</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Ceiling finishes</v>
+      </c>
+      <c r="G22" t="str">
         <v>All</v>
       </c>
-      <c r="E22" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="G22" t="str">
-        <v/>
-      </c>
       <c r="H22" t="str">
-        <v>Core</v>
+        <v/>
       </c>
       <c r="I22" t="str">
-        <v>Core</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J22" t="str">
-        <v>Core</v>
+        <v/>
       </c>
       <c r="K22" t="str">
         <v>Core</v>
       </c>
       <c r="L22" t="str">
-        <v>N/A</v>
+        <v>Core</v>
       </c>
       <c r="M22" t="str">
-        <v>N/A</v>
+        <v>Core</v>
       </c>
       <c r="N22" t="str">
-        <v>Optional</v>
+        <v>Core</v>
       </c>
       <c r="O22" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P22" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q22" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R22" t="str">
         <v/>
       </c>
     </row>
@@ -1648,39 +1937,48 @@
         <v>General fittings &amp; built-in joinery</v>
       </c>
       <c r="D23" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E23" t="str">
+        <v>4.1.1</v>
+      </c>
+      <c r="F23" t="str">
+        <v>General fittings, furnishings and equipment</v>
+      </c>
+      <c r="G23" t="str">
         <v>All</v>
       </c>
-      <c r="E23" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-      <c r="G23" t="str">
-        <v/>
-      </c>
       <c r="H23" t="str">
-        <v>Core</v>
+        <v/>
       </c>
       <c r="I23" t="str">
-        <v>Core</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J23" t="str">
-        <v>Core</v>
+        <v/>
       </c>
       <c r="K23" t="str">
         <v>Core</v>
       </c>
       <c r="L23" t="str">
-        <v>N/A</v>
+        <v>Core</v>
       </c>
       <c r="M23" t="str">
-        <v>N/A</v>
+        <v>Core</v>
       </c>
       <c r="N23" t="str">
-        <v>Optional</v>
+        <v>Core</v>
       </c>
       <c r="O23" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P23" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q23" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R23" t="str">
         <v/>
       </c>
     </row>
@@ -1695,39 +1993,48 @@
         <v>Sanitary fittings — commercial WC cubicle (per WC)</v>
       </c>
       <c r="D24" t="str">
+        <v>Per unit</v>
+      </c>
+      <c r="E24" t="str">
+        <v>5.1</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Sanitary installations</v>
+      </c>
+      <c r="G24" t="str">
         <v>Education, Office, Commercial</v>
       </c>
-      <c r="E24" t="str">
-        <v>per_nr</v>
-      </c>
-      <c r="F24">
-        <v>2</v>
-      </c>
-      <c r="G24" t="str">
-        <v/>
-      </c>
       <c r="H24" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I24" t="str">
-        <v>Optional</v>
+        <v>2 Finishes with minor services</v>
       </c>
       <c r="J24" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K24" t="str">
         <v>Optional</v>
       </c>
       <c r="L24" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M24" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N24" t="str">
         <v>Optional</v>
       </c>
       <c r="O24" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P24" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q24" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R24" t="str">
         <v/>
       </c>
     </row>
@@ -1742,39 +2049,48 @@
         <v>Sanitary fittings — clinical / HTM (per WC)</v>
       </c>
       <c r="D25" t="str">
+        <v>Per unit</v>
+      </c>
+      <c r="E25" t="str">
+        <v>5.1</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Sanitary installations</v>
+      </c>
+      <c r="G25" t="str">
         <v>Healthcare</v>
       </c>
-      <c r="E25" t="str">
-        <v>per_nr</v>
-      </c>
-      <c r="F25">
-        <v>2</v>
-      </c>
-      <c r="G25" t="str">
-        <v/>
-      </c>
       <c r="H25" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I25" t="str">
-        <v>Optional</v>
+        <v>2 Finishes with minor services</v>
       </c>
       <c r="J25" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K25" t="str">
         <v>Optional</v>
       </c>
       <c r="L25" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M25" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N25" t="str">
         <v>Optional</v>
       </c>
       <c r="O25" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P25" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q25" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R25" t="str">
         <v/>
       </c>
     </row>
@@ -1789,39 +2105,48 @@
         <v>Sanitary fittings — hotel guest-room ensuite (per bathroom)</v>
       </c>
       <c r="D26" t="str">
+        <v>Per unit</v>
+      </c>
+      <c r="E26" t="str">
+        <v>5.1</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Sanitary installations</v>
+      </c>
+      <c r="G26" t="str">
         <v>Hospitality (guest room)</v>
       </c>
-      <c r="E26" t="str">
-        <v>per_nr</v>
-      </c>
-      <c r="F26">
-        <v>2</v>
-      </c>
-      <c r="G26" t="str">
-        <v/>
-      </c>
       <c r="H26" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I26" t="str">
-        <v>Optional</v>
+        <v>2 Finishes with minor services</v>
       </c>
       <c r="J26" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K26" t="str">
         <v>Optional</v>
       </c>
       <c r="L26" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M26" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N26" t="str">
         <v>Optional</v>
       </c>
       <c r="O26" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P26" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q26" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R26" t="str">
         <v/>
       </c>
     </row>
@@ -1836,39 +2161,48 @@
         <v>Sanitary fittings — hotel public / back-of-house WC (per WC)</v>
       </c>
       <c r="D27" t="str">
+        <v>Per unit</v>
+      </c>
+      <c r="E27" t="str">
+        <v>5.1</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Sanitary installations</v>
+      </c>
+      <c r="G27" t="str">
         <v>Hospitality (public/BoH)</v>
       </c>
-      <c r="E27" t="str">
-        <v>per_nr</v>
-      </c>
-      <c r="F27">
-        <v>2</v>
-      </c>
-      <c r="G27" t="str">
-        <v/>
-      </c>
       <c r="H27" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I27" t="str">
-        <v>Optional</v>
+        <v>2 Finishes with minor services</v>
       </c>
       <c r="J27" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K27" t="str">
         <v>Optional</v>
       </c>
       <c r="L27" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M27" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N27" t="str">
         <v>Optional</v>
       </c>
       <c r="O27" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P27" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q27" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R27" t="str">
         <v/>
       </c>
     </row>
@@ -1883,39 +2217,48 @@
         <v>Sanitary fittings — residential bathroom / ensuite (per WC / wet room)</v>
       </c>
       <c r="D28" t="str">
+        <v>Per unit</v>
+      </c>
+      <c r="E28" t="str">
+        <v>5.1</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Sanitary installations</v>
+      </c>
+      <c r="G28" t="str">
         <v>Residential</v>
       </c>
-      <c r="E28" t="str">
-        <v>per_nr</v>
-      </c>
-      <c r="F28">
-        <v>2</v>
-      </c>
-      <c r="G28" t="str">
-        <v/>
-      </c>
       <c r="H28" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I28" t="str">
-        <v>Optional</v>
+        <v>2 Finishes with minor services</v>
       </c>
       <c r="J28" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K28" t="str">
         <v>Optional</v>
       </c>
       <c r="L28" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M28" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N28" t="str">
         <v>Optional</v>
       </c>
       <c r="O28" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P28" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q28" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R28" t="str">
         <v/>
       </c>
     </row>
@@ -1930,39 +2273,48 @@
         <v>Kitchen / break-out area</v>
       </c>
       <c r="D29" t="str">
+        <v>Per unit</v>
+      </c>
+      <c r="E29" t="str">
+        <v>4.1.2</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Domestic kitchen fittings and equipment</v>
+      </c>
+      <c r="G29" t="str">
         <v>All</v>
       </c>
-      <c r="E29" t="str">
-        <v>per_nr</v>
-      </c>
-      <c r="F29">
-        <v>2</v>
-      </c>
-      <c r="G29" t="str">
-        <v/>
-      </c>
       <c r="H29" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I29" t="str">
-        <v>Optional</v>
+        <v>2 Finishes with minor services</v>
       </c>
       <c r="J29" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K29" t="str">
         <v>Optional</v>
       </c>
       <c r="L29" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M29" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N29" t="str">
         <v>Optional</v>
       </c>
       <c r="O29" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P29" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q29" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R29" t="str">
         <v/>
       </c>
     </row>
@@ -1977,39 +2329,48 @@
         <v>Specialist equipment (lab/AV/med)</v>
       </c>
       <c r="D30" t="str">
+        <v>Lump sum</v>
+      </c>
+      <c r="E30" t="str">
+        <v>4.1.3</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Special purpose fittings, furnishings and equipment</v>
+      </c>
+      <c r="G30" t="str">
         <v>Non-Residential</v>
       </c>
-      <c r="E30" t="str">
-        <v>per_item</v>
-      </c>
-      <c r="F30">
-        <v>3</v>
-      </c>
-      <c r="G30" t="str">
-        <v/>
-      </c>
       <c r="H30" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I30" t="str">
-        <v>Optional</v>
+        <v>3 Full systems replacement</v>
       </c>
       <c r="J30" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K30" t="str">
         <v>Optional</v>
       </c>
       <c r="L30" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M30" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N30" t="str">
         <v>Optional</v>
       </c>
       <c r="O30" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P30" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q30" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R30" t="str">
         <v/>
       </c>
     </row>
@@ -2024,39 +2385,48 @@
         <v>Wayfinding &amp; signage</v>
       </c>
       <c r="D31" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E31" t="str">
+        <v>4.1.4</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Signs/notices</v>
+      </c>
+      <c r="G31" t="str">
         <v>All</v>
       </c>
-      <c r="E31" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F31">
-        <v>1</v>
-      </c>
-      <c r="G31" t="str">
-        <v/>
-      </c>
       <c r="H31" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I31" t="str">
-        <v>Optional</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J31" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K31" t="str">
         <v>Optional</v>
       </c>
       <c r="L31" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M31" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N31" t="str">
         <v>Optional</v>
       </c>
       <c r="O31" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P31" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q31" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R31" t="str">
         <v/>
       </c>
     </row>
@@ -2071,39 +2441,48 @@
         <v>Loose furniture &amp; FF&amp;E — residential</v>
       </c>
       <c r="D32" t="str">
+        <v>Per unit</v>
+      </c>
+      <c r="E32" t="str">
+        <v>4.1.1</v>
+      </c>
+      <c r="F32" t="str">
+        <v>General fittings, furnishings and equipment</v>
+      </c>
+      <c r="G32" t="str">
         <v>Residential</v>
       </c>
-      <c r="E32" t="str">
-        <v>per_nr</v>
-      </c>
-      <c r="F32">
-        <v>1</v>
-      </c>
-      <c r="G32" t="str">
-        <v/>
-      </c>
       <c r="H32" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I32" t="str">
-        <v>Optional</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J32" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K32" t="str">
         <v>Optional</v>
       </c>
       <c r="L32" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M32" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N32" t="str">
         <v>Optional</v>
       </c>
       <c r="O32" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P32" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q32" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R32" t="str">
         <v/>
       </c>
     </row>
@@ -2118,39 +2497,48 @@
         <v>Loose furniture &amp; FF&amp;E — office or education</v>
       </c>
       <c r="D33" t="str">
+        <v>Per unit</v>
+      </c>
+      <c r="E33" t="str">
+        <v>4.1.1</v>
+      </c>
+      <c r="F33" t="str">
+        <v>General fittings, furnishings and equipment</v>
+      </c>
+      <c r="G33" t="str">
         <v>Office, Education</v>
       </c>
-      <c r="E33" t="str">
-        <v>per_nr</v>
-      </c>
-      <c r="F33">
-        <v>1</v>
-      </c>
-      <c r="G33" t="str">
-        <v/>
-      </c>
       <c r="H33" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I33" t="str">
-        <v>Optional</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J33" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K33" t="str">
         <v>Optional</v>
       </c>
       <c r="L33" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M33" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N33" t="str">
         <v>Optional</v>
       </c>
       <c r="O33" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P33" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q33" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R33" t="str">
         <v/>
       </c>
     </row>
@@ -2165,39 +2553,48 @@
         <v>Loose furniture &amp; FF&amp;E — hospitality</v>
       </c>
       <c r="D34" t="str">
+        <v>Per unit</v>
+      </c>
+      <c r="E34" t="str">
+        <v>4.1.1</v>
+      </c>
+      <c r="F34" t="str">
+        <v>General fittings, furnishings and equipment</v>
+      </c>
+      <c r="G34" t="str">
         <v>Hospitality</v>
       </c>
-      <c r="E34" t="str">
-        <v>per_nr</v>
-      </c>
-      <c r="F34">
-        <v>1</v>
-      </c>
-      <c r="G34" t="str">
-        <v/>
-      </c>
       <c r="H34" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I34" t="str">
-        <v>Optional</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J34" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K34" t="str">
         <v>Optional</v>
       </c>
       <c r="L34" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M34" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N34" t="str">
         <v>Optional</v>
       </c>
       <c r="O34" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P34" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q34" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R34" t="str">
         <v/>
       </c>
     </row>
@@ -2212,25 +2609,25 @@
         <v>White goods — residential</v>
       </c>
       <c r="D35" t="str">
+        <v>Per unit</v>
+      </c>
+      <c r="E35" t="str">
+        <v>4.1.2</v>
+      </c>
+      <c r="F35" t="str">
+        <v>Domestic kitchen fittings and equipment</v>
+      </c>
+      <c r="G35" t="str">
         <v>Residential</v>
       </c>
-      <c r="E35" t="str">
-        <v>per_nr</v>
-      </c>
-      <c r="F35">
-        <v>1</v>
-      </c>
-      <c r="G35" t="str">
-        <v/>
-      </c>
       <c r="H35" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I35" t="str">
-        <v>N/A</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J35" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K35" t="str">
         <v>Optional</v>
@@ -2239,12 +2636,21 @@
         <v>N/A</v>
       </c>
       <c r="M35" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N35" t="str">
         <v>Optional</v>
       </c>
       <c r="O35" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P35" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q35" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R35" t="str">
         <v/>
       </c>
     </row>
@@ -2259,25 +2665,25 @@
         <v>Commercial catering kitchen equipment</v>
       </c>
       <c r="D36" t="str">
+        <v>Lump sum</v>
+      </c>
+      <c r="E36" t="str">
+        <v>4.1.3</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Special purpose fittings, furnishings and equipment</v>
+      </c>
+      <c r="G36" t="str">
         <v>Hospitality, Education, Healthcare</v>
       </c>
-      <c r="E36" t="str">
-        <v>per_item</v>
-      </c>
-      <c r="F36">
-        <v>3</v>
-      </c>
-      <c r="G36" t="str">
-        <v/>
-      </c>
       <c r="H36" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I36" t="str">
-        <v>N/A</v>
+        <v>3 Full systems replacement</v>
       </c>
       <c r="J36" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K36" t="str">
         <v>Optional</v>
@@ -2286,12 +2692,21 @@
         <v>N/A</v>
       </c>
       <c r="M36" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N36" t="str">
         <v>Optional</v>
       </c>
       <c r="O36" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P36" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q36" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R36" t="str">
         <v/>
       </c>
     </row>
@@ -2306,25 +2721,25 @@
         <v>Catering extract canopy system</v>
       </c>
       <c r="D37" t="str">
+        <v>Lump sum</v>
+      </c>
+      <c r="E37" t="str">
+        <v>5.7</v>
+      </c>
+      <c r="F37" t="str">
+        <v>Ventilation</v>
+      </c>
+      <c r="G37" t="str">
         <v>Hospitality, Education, Healthcare</v>
       </c>
-      <c r="E37" t="str">
-        <v>per_item</v>
-      </c>
-      <c r="F37">
-        <v>3</v>
-      </c>
-      <c r="G37" t="str">
-        <v/>
-      </c>
       <c r="H37" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I37" t="str">
-        <v>N/A</v>
+        <v>3 Full systems replacement</v>
       </c>
       <c r="J37" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K37" t="str">
         <v>Optional</v>
@@ -2333,12 +2748,21 @@
         <v>N/A</v>
       </c>
       <c r="M37" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N37" t="str">
         <v>Optional</v>
       </c>
       <c r="O37" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P37" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q37" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R37" t="str">
         <v/>
       </c>
     </row>
@@ -2353,25 +2777,25 @@
         <v>Bar counter and back bar</v>
       </c>
       <c r="D38" t="str">
+        <v>Lump sum</v>
+      </c>
+      <c r="E38" t="str">
+        <v>4.1.3</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Special purpose fittings, furnishings and equipment</v>
+      </c>
+      <c r="G38" t="str">
         <v>Hospitality</v>
       </c>
-      <c r="E38" t="str">
-        <v>per_item</v>
-      </c>
-      <c r="F38">
-        <v>1</v>
-      </c>
-      <c r="G38" t="str">
-        <v/>
-      </c>
       <c r="H38" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I38" t="str">
-        <v>N/A</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J38" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K38" t="str">
         <v>Optional</v>
@@ -2380,12 +2804,21 @@
         <v>N/A</v>
       </c>
       <c r="M38" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N38" t="str">
         <v>Optional</v>
       </c>
       <c r="O38" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P38" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q38" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R38" t="str">
         <v/>
       </c>
     </row>
@@ -2400,25 +2833,25 @@
         <v>Pallet racking and storage systems</v>
       </c>
       <c r="D39" t="str">
+        <v>Lump sum</v>
+      </c>
+      <c r="E39" t="str">
+        <v>4.1.3</v>
+      </c>
+      <c r="F39" t="str">
+        <v>Special purpose fittings, furnishings and equipment</v>
+      </c>
+      <c r="G39" t="str">
         <v>Industrial</v>
       </c>
-      <c r="E39" t="str">
-        <v>per_item</v>
-      </c>
-      <c r="F39">
-        <v>1</v>
-      </c>
-      <c r="G39" t="str">
-        <v/>
-      </c>
       <c r="H39" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I39" t="str">
-        <v>N/A</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J39" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K39" t="str">
         <v>Optional</v>
@@ -2427,12 +2860,21 @@
         <v>N/A</v>
       </c>
       <c r="M39" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N39" t="str">
         <v>Optional</v>
       </c>
       <c r="O39" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P39" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q39" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R39" t="str">
         <v/>
       </c>
     </row>
@@ -2447,25 +2889,25 @@
         <v>Dock levellers and dock seals</v>
       </c>
       <c r="D40" t="str">
+        <v>Per unit</v>
+      </c>
+      <c r="E40" t="str">
+        <v>4.1.3</v>
+      </c>
+      <c r="F40" t="str">
+        <v>Special purpose fittings, furnishings and equipment</v>
+      </c>
+      <c r="G40" t="str">
         <v>Industrial</v>
       </c>
-      <c r="E40" t="str">
-        <v>per_nr</v>
-      </c>
-      <c r="F40">
-        <v>4</v>
-      </c>
-      <c r="G40" t="str">
-        <v/>
-      </c>
       <c r="H40" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I40" t="str">
-        <v>N/A</v>
+        <v>4 Reconfiguration or full redesign</v>
       </c>
       <c r="J40" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K40" t="str">
         <v>Optional</v>
@@ -2474,12 +2916,21 @@
         <v>N/A</v>
       </c>
       <c r="M40" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N40" t="str">
         <v>Optional</v>
       </c>
       <c r="O40" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P40" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q40" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R40" t="str">
         <v/>
       </c>
     </row>
@@ -2494,39 +2945,48 @@
         <v>Roller shutter and sectional overhead doors</v>
       </c>
       <c r="D41" t="str">
+        <v>Per unit</v>
+      </c>
+      <c r="E41" t="str">
+        <v>2.6</v>
+      </c>
+      <c r="F41" t="str">
+        <v>Windows and external doors</v>
+      </c>
+      <c r="G41" t="str">
         <v>Industrial</v>
       </c>
-      <c r="E41" t="str">
-        <v>per_nr</v>
-      </c>
-      <c r="F41">
-        <v>1</v>
-      </c>
-      <c r="G41" t="str">
-        <v/>
-      </c>
       <c r="H41" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I41" t="str">
-        <v>Optional</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J41" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K41" t="str">
         <v>Optional</v>
       </c>
       <c r="L41" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M41" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N41" t="str">
         <v>Optional</v>
       </c>
       <c r="O41" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P41" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q41" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R41" t="str">
         <v/>
       </c>
     </row>
@@ -2541,25 +3001,25 @@
         <v>Cold store and refrigerated room</v>
       </c>
       <c r="D42" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E42" t="str">
+        <v>4.1.3</v>
+      </c>
+      <c r="F42" t="str">
+        <v>Special purpose fittings, furnishings and equipment</v>
+      </c>
+      <c r="G42" t="str">
         <v>Industrial, Hospitality</v>
       </c>
-      <c r="E42" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F42">
-        <v>3</v>
-      </c>
-      <c r="G42" t="str">
-        <v/>
-      </c>
       <c r="H42" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I42" t="str">
-        <v>N/A</v>
+        <v>3 Full systems replacement</v>
       </c>
       <c r="J42" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K42" t="str">
         <v>Optional</v>
@@ -2568,12 +3028,21 @@
         <v>N/A</v>
       </c>
       <c r="M42" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N42" t="str">
         <v>Optional</v>
       </c>
       <c r="O42" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P42" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q42" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R42" t="str">
         <v/>
       </c>
     </row>
@@ -2588,25 +3057,25 @@
         <v>Overhead crane and gantry</v>
       </c>
       <c r="D43" t="str">
+        <v>Lump sum</v>
+      </c>
+      <c r="E43" t="str">
+        <v>4.1.3</v>
+      </c>
+      <c r="F43" t="str">
+        <v>Special purpose fittings, furnishings and equipment</v>
+      </c>
+      <c r="G43" t="str">
         <v>Industrial</v>
       </c>
-      <c r="E43" t="str">
-        <v>per_item</v>
-      </c>
-      <c r="F43">
-        <v>4</v>
-      </c>
-      <c r="G43" t="str">
-        <v/>
-      </c>
       <c r="H43" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I43" t="str">
-        <v>N/A</v>
+        <v>4 Reconfiguration or full redesign</v>
       </c>
       <c r="J43" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K43" t="str">
         <v>Optional</v>
@@ -2615,12 +3084,21 @@
         <v>N/A</v>
       </c>
       <c r="M43" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N43" t="str">
         <v>Optional</v>
       </c>
       <c r="O43" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P43" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q43" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R43" t="str">
         <v/>
       </c>
     </row>
@@ -2635,25 +3113,25 @@
         <v>Medical gas pipeline</v>
       </c>
       <c r="D44" t="str">
+        <v>Per unit</v>
+      </c>
+      <c r="E44" t="str">
+        <v>5.13</v>
+      </c>
+      <c r="F44" t="str">
+        <v>Specialist installations</v>
+      </c>
+      <c r="G44" t="str">
         <v>Healthcare</v>
       </c>
-      <c r="E44" t="str">
-        <v>per_nr</v>
-      </c>
-      <c r="F44">
-        <v>3</v>
-      </c>
-      <c r="G44" t="str">
-        <v/>
-      </c>
       <c r="H44" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I44" t="str">
-        <v>N/A</v>
+        <v>3 Full systems replacement</v>
       </c>
       <c r="J44" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K44" t="str">
         <v>Optional</v>
@@ -2662,12 +3140,21 @@
         <v>N/A</v>
       </c>
       <c r="M44" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N44" t="str">
         <v>Optional</v>
       </c>
       <c r="O44" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P44" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q44" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R44" t="str">
         <v/>
       </c>
     </row>
@@ -2682,25 +3169,25 @@
         <v>Clinical furniture</v>
       </c>
       <c r="D45" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E45" t="str">
+        <v>4.1.3</v>
+      </c>
+      <c r="F45" t="str">
+        <v>Special purpose fittings, furnishings and equipment</v>
+      </c>
+      <c r="G45" t="str">
         <v>Healthcare</v>
       </c>
-      <c r="E45" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F45">
-        <v>1</v>
-      </c>
-      <c r="G45" t="str">
-        <v/>
-      </c>
       <c r="H45" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I45" t="str">
-        <v>N/A</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J45" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K45" t="str">
         <v>Optional</v>
@@ -2709,12 +3196,21 @@
         <v>N/A</v>
       </c>
       <c r="M45" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N45" t="str">
         <v>Optional</v>
       </c>
       <c r="O45" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P45" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q45" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R45" t="str">
         <v/>
       </c>
     </row>
@@ -2729,25 +3225,25 @@
         <v>Laboratory benching</v>
       </c>
       <c r="D46" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E46" t="str">
+        <v>4.1.3</v>
+      </c>
+      <c r="F46" t="str">
+        <v>Special purpose fittings, furnishings and equipment</v>
+      </c>
+      <c r="G46" t="str">
         <v>Education, Healthcare</v>
       </c>
-      <c r="E46" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F46">
-        <v>1</v>
-      </c>
-      <c r="G46" t="str">
-        <v/>
-      </c>
       <c r="H46" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I46" t="str">
-        <v>N/A</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J46" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K46" t="str">
         <v>Optional</v>
@@ -2756,12 +3252,21 @@
         <v>N/A</v>
       </c>
       <c r="M46" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N46" t="str">
         <v>Optional</v>
       </c>
       <c r="O46" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P46" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q46" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R46" t="str">
         <v/>
       </c>
     </row>
@@ -2776,25 +3281,25 @@
         <v>Fume cupboards</v>
       </c>
       <c r="D47" t="str">
+        <v>Per unit</v>
+      </c>
+      <c r="E47" t="str">
+        <v>4.1.3</v>
+      </c>
+      <c r="F47" t="str">
+        <v>Special purpose fittings, furnishings and equipment</v>
+      </c>
+      <c r="G47" t="str">
         <v>Education, Healthcare</v>
       </c>
-      <c r="E47" t="str">
-        <v>per_nr</v>
-      </c>
-      <c r="F47">
-        <v>3</v>
-      </c>
-      <c r="G47" t="str">
-        <v/>
-      </c>
       <c r="H47" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I47" t="str">
-        <v>N/A</v>
+        <v>3 Full systems replacement</v>
       </c>
       <c r="J47" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K47" t="str">
         <v>Optional</v>
@@ -2803,12 +3308,21 @@
         <v>N/A</v>
       </c>
       <c r="M47" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N47" t="str">
         <v>Optional</v>
       </c>
       <c r="O47" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P47" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q47" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R47" t="str">
         <v/>
       </c>
     </row>
@@ -2823,25 +3337,25 @@
         <v>AV and presentation system</v>
       </c>
       <c r="D48" t="str">
+        <v>Per unit</v>
+      </c>
+      <c r="E48" t="str">
+        <v>5.12</v>
+      </c>
+      <c r="F48" t="str">
+        <v>Communication, security and control systems</v>
+      </c>
+      <c r="G48" t="str">
         <v>Education, Office, Commercial</v>
       </c>
-      <c r="E48" t="str">
-        <v>per_nr</v>
-      </c>
-      <c r="F48">
-        <v>2</v>
-      </c>
-      <c r="G48" t="str">
-        <v/>
-      </c>
       <c r="H48" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I48" t="str">
-        <v>N/A</v>
+        <v>2 Finishes with minor services</v>
       </c>
       <c r="J48" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K48" t="str">
         <v>Optional</v>
@@ -2850,12 +3364,21 @@
         <v>N/A</v>
       </c>
       <c r="M48" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N48" t="str">
         <v>Optional</v>
       </c>
       <c r="O48" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P48" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q48" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R48" t="str">
         <v/>
       </c>
     </row>
@@ -2870,25 +3393,25 @@
         <v>Display units and merchandising fixtures</v>
       </c>
       <c r="D49" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E49" t="str">
+        <v>4.1.3</v>
+      </c>
+      <c r="F49" t="str">
+        <v>Special purpose fittings, furnishings and equipment</v>
+      </c>
+      <c r="G49" t="str">
         <v>Retail</v>
       </c>
-      <c r="E49" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F49">
-        <v>1</v>
-      </c>
-      <c r="G49" t="str">
-        <v/>
-      </c>
       <c r="H49" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I49" t="str">
-        <v>N/A</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J49" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K49" t="str">
         <v>Optional</v>
@@ -2897,12 +3420,21 @@
         <v>N/A</v>
       </c>
       <c r="M49" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N49" t="str">
         <v>Optional</v>
       </c>
       <c r="O49" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P49" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q49" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R49" t="str">
         <v/>
       </c>
     </row>
@@ -2917,25 +3449,25 @@
         <v>Sales counters and till positions</v>
       </c>
       <c r="D50" t="str">
+        <v>Per unit</v>
+      </c>
+      <c r="E50" t="str">
+        <v>4.1.3</v>
+      </c>
+      <c r="F50" t="str">
+        <v>Special purpose fittings, furnishings and equipment</v>
+      </c>
+      <c r="G50" t="str">
         <v>Retail</v>
       </c>
-      <c r="E50" t="str">
-        <v>per_nr</v>
-      </c>
-      <c r="F50">
-        <v>1</v>
-      </c>
-      <c r="G50" t="str">
-        <v/>
-      </c>
       <c r="H50" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I50" t="str">
-        <v>N/A</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J50" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K50" t="str">
         <v>Optional</v>
@@ -2944,12 +3476,21 @@
         <v>N/A</v>
       </c>
       <c r="M50" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N50" t="str">
         <v>Optional</v>
       </c>
       <c r="O50" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P50" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q50" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R50" t="str">
         <v/>
       </c>
     </row>
@@ -2964,25 +3505,25 @@
         <v>Fitting rooms</v>
       </c>
       <c r="D51" t="str">
+        <v>Per unit</v>
+      </c>
+      <c r="E51" t="str">
+        <v>4.1.3</v>
+      </c>
+      <c r="F51" t="str">
+        <v>Special purpose fittings, furnishings and equipment</v>
+      </c>
+      <c r="G51" t="str">
         <v>Retail</v>
       </c>
-      <c r="E51" t="str">
-        <v>per_nr</v>
-      </c>
-      <c r="F51">
-        <v>2</v>
-      </c>
-      <c r="G51" t="str">
-        <v/>
-      </c>
       <c r="H51" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I51" t="str">
-        <v>N/A</v>
+        <v>2 Finishes with minor services</v>
       </c>
       <c r="J51" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K51" t="str">
         <v>Optional</v>
@@ -2991,12 +3532,21 @@
         <v>N/A</v>
       </c>
       <c r="M51" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N51" t="str">
         <v>Optional</v>
       </c>
       <c r="O51" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P51" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q51" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R51" t="str">
         <v/>
       </c>
     </row>
@@ -3011,25 +3561,25 @@
         <v>EAS electronic article surveillance system</v>
       </c>
       <c r="D52" t="str">
+        <v>Lump sum</v>
+      </c>
+      <c r="E52" t="str">
+        <v>5.12</v>
+      </c>
+      <c r="F52" t="str">
+        <v>Communication, security and control systems</v>
+      </c>
+      <c r="G52" t="str">
         <v>Retail</v>
       </c>
-      <c r="E52" t="str">
-        <v>per_item</v>
-      </c>
-      <c r="F52">
-        <v>2</v>
-      </c>
-      <c r="G52" t="str">
-        <v/>
-      </c>
       <c r="H52" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I52" t="str">
-        <v>N/A</v>
+        <v>2 Finishes with minor services</v>
       </c>
       <c r="J52" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K52" t="str">
         <v>Optional</v>
@@ -3038,12 +3588,21 @@
         <v>N/A</v>
       </c>
       <c r="M52" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N52" t="str">
         <v>Optional</v>
       </c>
       <c r="O52" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P52" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q52" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R52" t="str">
         <v/>
       </c>
     </row>
@@ -3058,25 +3617,25 @@
         <v>Gym equipment</v>
       </c>
       <c r="D53" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E53" t="str">
+        <v>4.1.3</v>
+      </c>
+      <c r="F53" t="str">
+        <v>Special purpose fittings, furnishings and equipment</v>
+      </c>
+      <c r="G53" t="str">
         <v>Sports</v>
       </c>
-      <c r="E53" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F53">
-        <v>1</v>
-      </c>
-      <c r="G53" t="str">
-        <v/>
-      </c>
       <c r="H53" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I53" t="str">
-        <v>N/A</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J53" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K53" t="str">
         <v>Optional</v>
@@ -3085,12 +3644,21 @@
         <v>N/A</v>
       </c>
       <c r="M53" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N53" t="str">
         <v>Optional</v>
       </c>
       <c r="O53" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P53" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q53" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R53" t="str">
         <v/>
       </c>
     </row>
@@ -3105,25 +3673,25 @@
         <v>Spectator seating and bleachers</v>
       </c>
       <c r="D54" t="str">
+        <v>Per unit</v>
+      </c>
+      <c r="E54" t="str">
+        <v>4.1.3</v>
+      </c>
+      <c r="F54" t="str">
+        <v>Special purpose fittings, furnishings and equipment</v>
+      </c>
+      <c r="G54" t="str">
         <v>Sports</v>
       </c>
-      <c r="E54" t="str">
-        <v>per_nr</v>
-      </c>
-      <c r="F54">
-        <v>4</v>
-      </c>
-      <c r="G54" t="str">
-        <v/>
-      </c>
       <c r="H54" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I54" t="str">
-        <v>N/A</v>
+        <v>4 Reconfiguration or full redesign</v>
       </c>
       <c r="J54" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K54" t="str">
         <v>Optional</v>
@@ -3132,12 +3700,21 @@
         <v>N/A</v>
       </c>
       <c r="M54" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N54" t="str">
         <v>Optional</v>
       </c>
       <c r="O54" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P54" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q54" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R54" t="str">
         <v/>
       </c>
     </row>
@@ -3152,25 +3729,25 @@
         <v>Changing room lockers and benching</v>
       </c>
       <c r="D55" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E55" t="str">
+        <v>4.1.3</v>
+      </c>
+      <c r="F55" t="str">
+        <v>Special purpose fittings, furnishings and equipment</v>
+      </c>
+      <c r="G55" t="str">
         <v>Sports</v>
       </c>
-      <c r="E55" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F55">
-        <v>1</v>
-      </c>
-      <c r="G55" t="str">
-        <v/>
-      </c>
       <c r="H55" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I55" t="str">
-        <v>N/A</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J55" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K55" t="str">
         <v>Optional</v>
@@ -3179,12 +3756,21 @@
         <v>N/A</v>
       </c>
       <c r="M55" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N55" t="str">
         <v>Optional</v>
       </c>
       <c r="O55" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P55" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q55" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R55" t="str">
         <v/>
       </c>
     </row>
@@ -3199,39 +3785,48 @@
         <v>Toilet cubicle partitions — solid grade laminate / solid surface (per cubicle)</v>
       </c>
       <c r="D56" t="str">
+        <v>Per unit</v>
+      </c>
+      <c r="E56" t="str">
+        <v>2.7</v>
+      </c>
+      <c r="F56" t="str">
+        <v>Internal walls and partitions</v>
+      </c>
+      <c r="G56" t="str">
         <v>Non-Residential</v>
       </c>
-      <c r="E56" t="str">
-        <v>per_nr</v>
-      </c>
-      <c r="F56">
-        <v>2</v>
-      </c>
-      <c r="G56" t="str">
-        <v/>
-      </c>
       <c r="H56" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I56" t="str">
-        <v>Optional</v>
+        <v>2 Finishes with minor services</v>
       </c>
       <c r="J56" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K56" t="str">
         <v>Optional</v>
       </c>
       <c r="L56" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M56" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N56" t="str">
         <v>Optional</v>
       </c>
       <c r="O56" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P56" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q56" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R56" t="str">
         <v/>
       </c>
     </row>
@@ -3246,39 +3841,48 @@
         <v>Vanity counter, basins surround &amp; mirror wall (per run)</v>
       </c>
       <c r="D57" t="str">
+        <v>Lump sum</v>
+      </c>
+      <c r="E57" t="str">
+        <v>4.1.1</v>
+      </c>
+      <c r="F57" t="str">
+        <v>General fittings, furnishings and equipment</v>
+      </c>
+      <c r="G57" t="str">
         <v>Hospitality, Office, Healthcare</v>
       </c>
-      <c r="E57" t="str">
-        <v>per_item</v>
-      </c>
-      <c r="F57">
-        <v>2</v>
-      </c>
-      <c r="G57" t="str">
-        <v/>
-      </c>
       <c r="H57" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I57" t="str">
-        <v>Optional</v>
+        <v>2 Finishes with minor services</v>
       </c>
       <c r="J57" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K57" t="str">
         <v>Optional</v>
       </c>
       <c r="L57" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M57" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N57" t="str">
         <v>Optional</v>
       </c>
       <c r="O57" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P57" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q57" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R57" t="str">
         <v/>
       </c>
     </row>
@@ -3293,39 +3897,48 @@
         <v>Sanitary plumbing (1st &amp; 2nd fix)</v>
       </c>
       <c r="D58" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E58" t="str">
+        <v>5.4</v>
+      </c>
+      <c r="F58" t="str">
+        <v>Water installations</v>
+      </c>
+      <c r="G58" t="str">
         <v>All</v>
       </c>
-      <c r="E58" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F58">
-        <v>2</v>
-      </c>
-      <c r="G58" t="str">
-        <v/>
-      </c>
       <c r="H58" t="str">
-        <v>Core</v>
+        <v/>
       </c>
       <c r="I58" t="str">
-        <v>Core</v>
+        <v>2 Finishes with minor services</v>
       </c>
       <c r="J58" t="str">
-        <v>Core</v>
+        <v/>
       </c>
       <c r="K58" t="str">
         <v>Core</v>
       </c>
       <c r="L58" t="str">
-        <v>N/A</v>
+        <v>Core</v>
       </c>
       <c r="M58" t="str">
-        <v>N/A</v>
+        <v>Core</v>
       </c>
       <c r="N58" t="str">
-        <v>Optional</v>
+        <v>Core</v>
       </c>
       <c r="O58" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P58" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q58" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R58" t="str">
         <v/>
       </c>
     </row>
@@ -3340,25 +3953,25 @@
         <v>Mechanical second fix</v>
       </c>
       <c r="D59" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E59" t="str">
+        <v>5.4</v>
+      </c>
+      <c r="F59" t="str">
+        <v>Water installations</v>
+      </c>
+      <c r="G59" t="str">
         <v>All</v>
       </c>
-      <c r="E59" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F59">
-        <v>1</v>
-      </c>
-      <c r="G59" t="str">
-        <v/>
-      </c>
       <c r="H59" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="I59" t="str">
-        <v>N/A</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J59" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="K59" t="str">
         <v>N/A</v>
@@ -3373,6 +3986,15 @@
         <v>N/A</v>
       </c>
       <c r="O59" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P59" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q59" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="R59" t="str">
         <v/>
       </c>
     </row>
@@ -3387,39 +4009,48 @@
         <v>Heating &amp; hot water (LTHW/heat pump)</v>
       </c>
       <c r="D60" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E60" t="str">
+        <v>5.5</v>
+      </c>
+      <c r="F60" t="str">
+        <v>Heat source</v>
+      </c>
+      <c r="G60" t="str">
         <v>All</v>
       </c>
-      <c r="E60" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F60">
-        <v>3</v>
-      </c>
-      <c r="G60" t="str">
-        <v/>
-      </c>
       <c r="H60" t="str">
-        <v>Core</v>
+        <v/>
       </c>
       <c r="I60" t="str">
-        <v>Core</v>
+        <v>3 Full systems replacement</v>
       </c>
       <c r="J60" t="str">
-        <v>Core</v>
+        <v/>
       </c>
       <c r="K60" t="str">
         <v>Core</v>
       </c>
       <c r="L60" t="str">
-        <v>N/A</v>
+        <v>Core</v>
       </c>
       <c r="M60" t="str">
-        <v>N/A</v>
+        <v>Core</v>
       </c>
       <c r="N60" t="str">
-        <v>Optional</v>
+        <v>Core</v>
       </c>
       <c r="O60" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P60" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q60" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R60" t="str">
         <v/>
       </c>
     </row>
@@ -3434,25 +4065,25 @@
         <v>Gas boiler / plant — like-for-like replacement only (no new pipework)</v>
       </c>
       <c r="D61" t="str">
+        <v>Lump sum</v>
+      </c>
+      <c r="E61" t="str">
+        <v>5.5</v>
+      </c>
+      <c r="F61" t="str">
+        <v>Heat source</v>
+      </c>
+      <c r="G61" t="str">
         <v>All</v>
       </c>
-      <c r="E61" t="str">
-        <v>per_item</v>
-      </c>
-      <c r="F61">
-        <v>2</v>
-      </c>
-      <c r="G61" t="str">
-        <v/>
-      </c>
       <c r="H61" t="str">
-        <v>n/a — folded into parent</v>
+        <v/>
       </c>
       <c r="I61" t="str">
-        <v>n/a — folded into parent</v>
+        <v>2 Finishes with minor services</v>
       </c>
       <c r="J61" t="str">
-        <v>n/a — folded into parent</v>
+        <v/>
       </c>
       <c r="K61" t="str">
         <v>n/a — folded into parent</v>
@@ -3467,6 +4098,15 @@
         <v>n/a — folded into parent</v>
       </c>
       <c r="O61" t="str">
+        <v>n/a — folded into parent</v>
+      </c>
+      <c r="P61" t="str">
+        <v>n/a — folded into parent</v>
+      </c>
+      <c r="Q61" t="str">
+        <v>n/a — folded into parent</v>
+      </c>
+      <c r="R61" t="str">
         <v/>
       </c>
     </row>
@@ -3481,39 +4121,48 @@
         <v>Ventilation &amp; air handling</v>
       </c>
       <c r="D62" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E62" t="str">
+        <v>5.7</v>
+      </c>
+      <c r="F62" t="str">
+        <v>Ventilation</v>
+      </c>
+      <c r="G62" t="str">
         <v>All</v>
       </c>
-      <c r="E62" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F62">
-        <v>3</v>
-      </c>
-      <c r="G62" t="str">
-        <v/>
-      </c>
       <c r="H62" t="str">
+        <v/>
+      </c>
+      <c r="I62" t="str">
+        <v>3 Full systems replacement</v>
+      </c>
+      <c r="J62" t="str">
+        <v/>
+      </c>
+      <c r="K62" t="str">
         <v>Core</v>
       </c>
-      <c r="I62" t="str">
+      <c r="L62" t="str">
         <v>Core</v>
       </c>
-      <c r="J62" t="str">
-        <v>Optional</v>
-      </c>
-      <c r="K62" t="str">
-        <v>Optional</v>
-      </c>
-      <c r="L62" t="str">
-        <v>N/A</v>
-      </c>
       <c r="M62" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N62" t="str">
         <v>Optional</v>
       </c>
       <c r="O62" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P62" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q62" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R62" t="str">
         <v/>
       </c>
     </row>
@@ -3528,39 +4177,48 @@
         <v>Air conditioning &amp; cooling</v>
       </c>
       <c r="D63" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E63" t="str">
+        <v>5.6</v>
+      </c>
+      <c r="F63" t="str">
+        <v>Space heating and air conditioning</v>
+      </c>
+      <c r="G63" t="str">
         <v>All</v>
       </c>
-      <c r="E63" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F63">
-        <v>3</v>
-      </c>
-      <c r="G63" t="str">
-        <v/>
-      </c>
       <c r="H63" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I63" t="str">
-        <v>Optional</v>
+        <v>3 Full systems replacement</v>
       </c>
       <c r="J63" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K63" t="str">
         <v>Optional</v>
       </c>
       <c r="L63" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M63" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N63" t="str">
         <v>Optional</v>
       </c>
       <c r="O63" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P63" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q63" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R63" t="str">
         <v/>
       </c>
     </row>
@@ -3575,25 +4233,25 @@
         <v>Gas installation</v>
       </c>
       <c r="D64" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E64" t="str">
+        <v>5.9</v>
+      </c>
+      <c r="F64" t="str">
+        <v>Fuel installations</v>
+      </c>
+      <c r="G64" t="str">
         <v>All</v>
       </c>
-      <c r="E64" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F64">
-        <v>3</v>
-      </c>
-      <c r="G64" t="str">
-        <v/>
-      </c>
       <c r="H64" t="str">
-        <v>n/a — folded into parent</v>
+        <v/>
       </c>
       <c r="I64" t="str">
-        <v>n/a — folded into parent</v>
+        <v>3 Full systems replacement</v>
       </c>
       <c r="J64" t="str">
-        <v>n/a — folded into parent</v>
+        <v/>
       </c>
       <c r="K64" t="str">
         <v>n/a — folded into parent</v>
@@ -3608,6 +4266,15 @@
         <v>n/a — folded into parent</v>
       </c>
       <c r="O64" t="str">
+        <v>n/a — folded into parent</v>
+      </c>
+      <c r="P64" t="str">
+        <v>n/a — folded into parent</v>
+      </c>
+      <c r="Q64" t="str">
+        <v>n/a — folded into parent</v>
+      </c>
+      <c r="R64" t="str">
         <v/>
       </c>
     </row>
@@ -3622,39 +4289,48 @@
         <v>Sprinkler / fire suppression</v>
       </c>
       <c r="D65" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E65" t="str">
+        <v>5.11</v>
+      </c>
+      <c r="F65" t="str">
+        <v>Fire and lightning protection</v>
+      </c>
+      <c r="G65" t="str">
         <v>All</v>
       </c>
-      <c r="E65" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F65">
-        <v>3</v>
-      </c>
-      <c r="G65" t="str">
-        <v/>
-      </c>
       <c r="H65" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I65" t="str">
-        <v>Optional</v>
+        <v>3 Full systems replacement</v>
       </c>
       <c r="J65" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K65" t="str">
         <v>Optional</v>
       </c>
       <c r="L65" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M65" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N65" t="str">
         <v>Optional</v>
       </c>
       <c r="O65" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P65" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q65" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R65" t="str">
         <v/>
       </c>
     </row>
@@ -3669,39 +4345,48 @@
         <v>Electrical distribution &amp; switchgear</v>
       </c>
       <c r="D66" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E66" t="str">
+        <v>5.8</v>
+      </c>
+      <c r="F66" t="str">
+        <v>Electrical installations</v>
+      </c>
+      <c r="G66" t="str">
         <v>All</v>
       </c>
-      <c r="E66" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F66">
-        <v>3</v>
-      </c>
-      <c r="G66" t="str">
-        <v/>
-      </c>
       <c r="H66" t="str">
+        <v/>
+      </c>
+      <c r="I66" t="str">
+        <v>3 Full systems replacement</v>
+      </c>
+      <c r="J66" t="str">
+        <v/>
+      </c>
+      <c r="K66" t="str">
         <v>Core</v>
       </c>
-      <c r="I66" t="str">
+      <c r="L66" t="str">
         <v>Core</v>
       </c>
-      <c r="J66" t="str">
-        <v>Optional</v>
-      </c>
-      <c r="K66" t="str">
-        <v>Optional</v>
-      </c>
-      <c r="L66" t="str">
-        <v>N/A</v>
-      </c>
       <c r="M66" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N66" t="str">
         <v>Optional</v>
       </c>
       <c r="O66" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P66" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q66" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R66" t="str">
         <v/>
       </c>
     </row>
@@ -3716,39 +4401,48 @@
         <v>Sub-distribution and containment — sub-DBs, cable tray, trunking, busbar</v>
       </c>
       <c r="D67" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E67" t="str">
+        <v>5.8</v>
+      </c>
+      <c r="F67" t="str">
+        <v>Electrical installations</v>
+      </c>
+      <c r="G67" t="str">
         <v>Non-Residential</v>
       </c>
-      <c r="E67" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F67">
-        <v>3</v>
-      </c>
-      <c r="G67" t="str">
-        <v/>
-      </c>
       <c r="H67" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I67" t="str">
-        <v>Optional</v>
+        <v>3 Full systems replacement</v>
       </c>
       <c r="J67" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K67" t="str">
         <v>Optional</v>
       </c>
       <c r="L67" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M67" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N67" t="str">
         <v>Optional</v>
       </c>
       <c r="O67" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P67" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q67" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R67" t="str">
         <v/>
       </c>
     </row>
@@ -3763,25 +4457,25 @@
         <v>Electrical wiring (1st &amp; 2nd fix)</v>
       </c>
       <c r="D68" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E68" t="str">
+        <v>5.8</v>
+      </c>
+      <c r="F68" t="str">
+        <v>Electrical installations</v>
+      </c>
+      <c r="G68" t="str">
         <v>All</v>
       </c>
-      <c r="E68" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F68">
-        <v>2</v>
-      </c>
-      <c r="G68" t="str">
-        <v/>
-      </c>
       <c r="H68" t="str">
-        <v>n/a — folded into parent</v>
+        <v/>
       </c>
       <c r="I68" t="str">
-        <v>n/a — folded into parent</v>
+        <v>2 Finishes with minor services</v>
       </c>
       <c r="J68" t="str">
-        <v>n/a — folded into parent</v>
+        <v/>
       </c>
       <c r="K68" t="str">
         <v>n/a — folded into parent</v>
@@ -3796,6 +4490,15 @@
         <v>n/a — folded into parent</v>
       </c>
       <c r="O68" t="str">
+        <v>n/a — folded into parent</v>
+      </c>
+      <c r="P68" t="str">
+        <v>n/a — folded into parent</v>
+      </c>
+      <c r="Q68" t="str">
+        <v>n/a — folded into parent</v>
+      </c>
+      <c r="R68" t="str">
         <v/>
       </c>
     </row>
@@ -3810,39 +4513,48 @@
         <v>Electrical 1st fix wiring only — new circuit cables; existing sockets/luminaires retained</v>
       </c>
       <c r="D69" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E69" t="str">
+        <v>5.8</v>
+      </c>
+      <c r="F69" t="str">
+        <v>Electrical installations</v>
+      </c>
+      <c r="G69" t="str">
         <v>All</v>
       </c>
-      <c r="E69" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F69">
-        <v>3</v>
-      </c>
-      <c r="G69" t="str">
-        <v/>
-      </c>
       <c r="H69" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="I69" t="str">
-        <v>N/A</v>
+        <v>3 Full systems replacement</v>
       </c>
       <c r="J69" t="str">
+        <v/>
+      </c>
+      <c r="K69" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L69" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="M69" t="str">
         <v>Core</v>
       </c>
-      <c r="K69" t="str">
+      <c r="N69" t="str">
         <v>Core</v>
       </c>
-      <c r="L69" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="M69" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="N69" t="str">
-        <v>Optional</v>
-      </c>
       <c r="O69" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P69" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q69" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R69" t="str">
         <v/>
       </c>
     </row>
@@ -3857,39 +4569,48 @@
         <v>Electrical 2nd fix only — replacement sockets, switches, FCUs; existing wiring reused</v>
       </c>
       <c r="D70" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E70" t="str">
+        <v>5.8</v>
+      </c>
+      <c r="F70" t="str">
+        <v>Electrical installations</v>
+      </c>
+      <c r="G70" t="str">
         <v>All</v>
       </c>
-      <c r="E70" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F70">
-        <v>2</v>
-      </c>
-      <c r="G70" t="str">
-        <v/>
-      </c>
       <c r="H70" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="I70" t="str">
-        <v>N/A</v>
+        <v>2 Finishes with minor services</v>
       </c>
       <c r="J70" t="str">
+        <v/>
+      </c>
+      <c r="K70" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L70" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="M70" t="str">
         <v>Core</v>
       </c>
-      <c r="K70" t="str">
+      <c r="N70" t="str">
         <v>Core</v>
       </c>
-      <c r="L70" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="M70" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="N70" t="str">
-        <v>Optional</v>
-      </c>
       <c r="O70" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P70" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q70" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R70" t="str">
         <v/>
       </c>
     </row>
@@ -3904,39 +4625,48 @@
         <v>2nd fix lighting — new luminaires, layout, controls and occupancy sensors</v>
       </c>
       <c r="D71" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E71" t="str">
+        <v>5.8</v>
+      </c>
+      <c r="F71" t="str">
+        <v>Electrical installations</v>
+      </c>
+      <c r="G71" t="str">
         <v>All</v>
       </c>
-      <c r="E71" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F71">
-        <v>2</v>
-      </c>
-      <c r="G71" t="str">
-        <v/>
-      </c>
       <c r="H71" t="str">
-        <v>Core</v>
+        <v/>
       </c>
       <c r="I71" t="str">
-        <v>Core</v>
+        <v>2 Finishes with minor services</v>
       </c>
       <c r="J71" t="str">
-        <v>Core</v>
+        <v/>
       </c>
       <c r="K71" t="str">
         <v>Core</v>
       </c>
       <c r="L71" t="str">
-        <v>N/A</v>
+        <v>Core</v>
       </c>
       <c r="M71" t="str">
-        <v>N/A</v>
+        <v>Core</v>
       </c>
       <c r="N71" t="str">
-        <v>Optional</v>
+        <v>Core</v>
       </c>
       <c r="O71" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P71" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q71" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R71" t="str">
         <v/>
       </c>
     </row>
@@ -3951,39 +4681,48 @@
         <v>Fire alarm system — detection, call points, sounders, visual alarms and panel (L1–L3)</v>
       </c>
       <c r="D72" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E72" t="str">
+        <v>5.12</v>
+      </c>
+      <c r="F72" t="str">
+        <v>Communication, security and control systems</v>
+      </c>
+      <c r="G72" t="str">
         <v>All</v>
       </c>
-      <c r="E72" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F72">
-        <v>3</v>
-      </c>
-      <c r="G72" t="str">
-        <v/>
-      </c>
       <c r="H72" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I72" t="str">
-        <v>Optional</v>
+        <v>3 Full systems replacement</v>
       </c>
       <c r="J72" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K72" t="str">
         <v>Optional</v>
       </c>
       <c r="L72" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M72" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N72" t="str">
         <v>Optional</v>
       </c>
       <c r="O72" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P72" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q72" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R72" t="str">
         <v/>
       </c>
     </row>
@@ -3998,39 +4737,48 @@
         <v>Emergency lighting — maintained and non-maintained luminaires, central test system</v>
       </c>
       <c r="D73" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E73" t="str">
+        <v>5.8</v>
+      </c>
+      <c r="F73" t="str">
+        <v>Electrical installations</v>
+      </c>
+      <c r="G73" t="str">
         <v>Non-Residential</v>
       </c>
-      <c r="E73" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F73">
-        <v>3</v>
-      </c>
-      <c r="G73" t="str">
-        <v/>
-      </c>
       <c r="H73" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I73" t="str">
-        <v>Optional</v>
+        <v>3 Full systems replacement</v>
       </c>
       <c r="J73" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K73" t="str">
         <v>Optional</v>
       </c>
       <c r="L73" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M73" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N73" t="str">
         <v>Optional</v>
       </c>
       <c r="O73" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P73" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q73" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R73" t="str">
         <v/>
       </c>
     </row>
@@ -4045,39 +4793,48 @@
         <v>External lighting (building-mounted)</v>
       </c>
       <c r="D74" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E74" t="str">
+        <v>5.8</v>
+      </c>
+      <c r="F74" t="str">
+        <v>Electrical installations</v>
+      </c>
+      <c r="G74" t="str">
         <v>All</v>
       </c>
-      <c r="E74" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F74">
-        <v>1</v>
-      </c>
-      <c r="G74" t="str">
-        <v/>
-      </c>
       <c r="H74" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I74" t="str">
-        <v>Optional</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J74" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K74" t="str">
         <v>Optional</v>
       </c>
       <c r="L74" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M74" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N74" t="str">
         <v>Optional</v>
       </c>
       <c r="O74" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P74" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q74" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R74" t="str">
         <v/>
       </c>
     </row>
@@ -4092,39 +4849,48 @@
         <v>Solar PV / renewables</v>
       </c>
       <c r="D75" t="str">
+        <v>Per kWp</v>
+      </c>
+      <c r="E75" t="str">
+        <v>5.13</v>
+      </c>
+      <c r="F75" t="str">
+        <v>Specialist installations</v>
+      </c>
+      <c r="G75" t="str">
         <v>All</v>
       </c>
-      <c r="E75" t="str">
-        <v>per_kwp</v>
-      </c>
-      <c r="F75">
-        <v>3</v>
-      </c>
-      <c r="G75" t="str">
-        <v/>
-      </c>
       <c r="H75" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I75" t="str">
-        <v>Optional</v>
+        <v>3 Full systems replacement</v>
       </c>
       <c r="J75" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K75" t="str">
         <v>Optional</v>
       </c>
       <c r="L75" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M75" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N75" t="str">
         <v>Optional</v>
       </c>
       <c r="O75" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P75" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q75" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R75" t="str">
         <v/>
       </c>
     </row>
@@ -4139,39 +4905,48 @@
         <v>Battery energy storage (BESS)</v>
       </c>
       <c r="D76" t="str">
+        <v>Per kWh</v>
+      </c>
+      <c r="E76" t="str">
+        <v>5.13</v>
+      </c>
+      <c r="F76" t="str">
+        <v>Specialist installations</v>
+      </c>
+      <c r="G76" t="str">
         <v>All</v>
       </c>
-      <c r="E76" t="str">
-        <v>per_kwh</v>
-      </c>
-      <c r="F76">
-        <v>3</v>
-      </c>
-      <c r="G76" t="str">
-        <v/>
-      </c>
       <c r="H76" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I76" t="str">
-        <v>Optional</v>
+        <v>3 Full systems replacement</v>
       </c>
       <c r="J76" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K76" t="str">
         <v>Optional</v>
       </c>
       <c r="L76" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M76" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N76" t="str">
         <v>Optional</v>
       </c>
       <c r="O76" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P76" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q76" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R76" t="str">
         <v/>
       </c>
     </row>
@@ -4186,39 +4961,48 @@
         <v>Grid connection / DNO upgrade</v>
       </c>
       <c r="D77" t="str">
+        <v>Lump sum</v>
+      </c>
+      <c r="E77" t="str">
+        <v>8.7</v>
+      </c>
+      <c r="F77" t="str">
+        <v>External services</v>
+      </c>
+      <c r="G77" t="str">
         <v>Non-Residential</v>
       </c>
-      <c r="E77" t="str">
-        <v>per_item</v>
-      </c>
-      <c r="F77">
-        <v>3</v>
-      </c>
-      <c r="G77" t="str">
-        <v/>
-      </c>
       <c r="H77" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I77" t="str">
-        <v>Optional</v>
+        <v>3 Full systems replacement</v>
       </c>
       <c r="J77" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K77" t="str">
         <v>Optional</v>
       </c>
       <c r="L77" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M77" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N77" t="str">
         <v>Optional</v>
       </c>
       <c r="O77" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P77" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q77" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R77" t="str">
         <v/>
       </c>
     </row>
@@ -4233,39 +5017,48 @@
         <v>Building energy management (BEMS)</v>
       </c>
       <c r="D78" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E78" t="str">
+        <v>5.12</v>
+      </c>
+      <c r="F78" t="str">
+        <v>Communication, security and control systems</v>
+      </c>
+      <c r="G78" t="str">
         <v>Non-Residential</v>
       </c>
-      <c r="E78" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F78">
-        <v>3</v>
-      </c>
-      <c r="G78" t="str">
-        <v/>
-      </c>
       <c r="H78" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I78" t="str">
-        <v>Optional</v>
+        <v>3 Full systems replacement</v>
       </c>
       <c r="J78" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K78" t="str">
         <v>Optional</v>
       </c>
       <c r="L78" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M78" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N78" t="str">
         <v>Optional</v>
       </c>
       <c r="O78" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P78" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q78" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R78" t="str">
         <v/>
       </c>
     </row>
@@ -4280,39 +5073,48 @@
         <v>EV charging points</v>
       </c>
       <c r="D79" t="str">
+        <v>Per unit</v>
+      </c>
+      <c r="E79" t="str">
+        <v>5.13</v>
+      </c>
+      <c r="F79" t="str">
+        <v>Specialist installations</v>
+      </c>
+      <c r="G79" t="str">
         <v>All</v>
       </c>
-      <c r="E79" t="str">
-        <v>per_nr</v>
-      </c>
-      <c r="F79">
-        <v>3</v>
-      </c>
-      <c r="G79" t="str">
-        <v/>
-      </c>
       <c r="H79" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I79" t="str">
-        <v>Optional</v>
+        <v>3 Full systems replacement</v>
       </c>
       <c r="J79" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K79" t="str">
         <v>Optional</v>
       </c>
       <c r="L79" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M79" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N79" t="str">
         <v>Optional</v>
       </c>
       <c r="O79" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P79" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q79" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R79" t="str">
         <v/>
       </c>
     </row>
@@ -4327,39 +5129,48 @@
         <v>IT / data infrastructure (Cat6A)</v>
       </c>
       <c r="D80" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E80" t="str">
+        <v>5.12</v>
+      </c>
+      <c r="F80" t="str">
+        <v>Communication, security and control systems</v>
+      </c>
+      <c r="G80" t="str">
         <v>Non-Residential</v>
       </c>
-      <c r="E80" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F80">
-        <v>2</v>
-      </c>
-      <c r="G80" t="str">
-        <v/>
-      </c>
       <c r="H80" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I80" t="str">
-        <v>Optional</v>
+        <v>2 Finishes with minor services</v>
       </c>
       <c r="J80" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K80" t="str">
         <v>Optional</v>
       </c>
       <c r="L80" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M80" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N80" t="str">
         <v>Optional</v>
       </c>
       <c r="O80" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P80" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q80" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R80" t="str">
         <v/>
       </c>
     </row>
@@ -4374,39 +5185,48 @@
         <v>Access control &amp; CCTV / security</v>
       </c>
       <c r="D81" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E81" t="str">
+        <v>5.12</v>
+      </c>
+      <c r="F81" t="str">
+        <v>Communication, security and control systems</v>
+      </c>
+      <c r="G81" t="str">
         <v>Non-Residential</v>
       </c>
-      <c r="E81" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F81">
-        <v>3</v>
-      </c>
-      <c r="G81" t="str">
-        <v/>
-      </c>
       <c r="H81" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I81" t="str">
-        <v>Optional</v>
+        <v>3 Full systems replacement</v>
       </c>
       <c r="J81" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K81" t="str">
         <v>Optional</v>
       </c>
       <c r="L81" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M81" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N81" t="str">
         <v>Optional</v>
       </c>
       <c r="O81" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P81" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q81" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R81" t="str">
         <v/>
       </c>
     </row>
@@ -4421,39 +5241,48 @@
         <v>Lifts &amp; platform lifts</v>
       </c>
       <c r="D82" t="str">
+        <v>Per unit</v>
+      </c>
+      <c r="E82" t="str">
+        <v>5.10</v>
+      </c>
+      <c r="F82" t="str">
+        <v>Lift and conveyor installations</v>
+      </c>
+      <c r="G82" t="str">
         <v>All</v>
       </c>
-      <c r="E82" t="str">
-        <v>per_nr</v>
-      </c>
-      <c r="F82">
-        <v>3</v>
-      </c>
-      <c r="G82" t="str">
-        <v/>
-      </c>
       <c r="H82" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I82" t="str">
-        <v>Optional</v>
+        <v>3 Full systems replacement</v>
       </c>
       <c r="J82" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K82" t="str">
         <v>Optional</v>
       </c>
       <c r="L82" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M82" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N82" t="str">
         <v>Optional</v>
       </c>
       <c r="O82" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P82" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q82" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R82" t="str">
         <v/>
       </c>
     </row>
@@ -4468,39 +5297,48 @@
         <v>Builder's work in connection (BWIC)</v>
       </c>
       <c r="D83" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E83" t="str">
+        <v>5.14</v>
+      </c>
+      <c r="F83" t="str">
+        <v>Builder’s work in connection with services</v>
+      </c>
+      <c r="G83" t="str">
         <v>All</v>
       </c>
-      <c r="E83" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F83">
-        <v>3</v>
-      </c>
-      <c r="G83" t="str">
-        <v/>
-      </c>
       <c r="H83" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I83" t="str">
-        <v>Optional</v>
+        <v>3 Full systems replacement</v>
       </c>
       <c r="J83" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K83" t="str">
         <v>Optional</v>
       </c>
       <c r="L83" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M83" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N83" t="str">
         <v>Optional</v>
       </c>
       <c r="O83" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P83" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q83" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R83" t="str">
         <v/>
       </c>
     </row>
@@ -4515,25 +5353,25 @@
         <v>Compressed air ring main</v>
       </c>
       <c r="D84" t="str">
+        <v>Lump sum</v>
+      </c>
+      <c r="E84" t="str">
+        <v>5.13</v>
+      </c>
+      <c r="F84" t="str">
+        <v>Specialist installations</v>
+      </c>
+      <c r="G84" t="str">
         <v>Industrial, Education</v>
       </c>
-      <c r="E84" t="str">
-        <v>per_item</v>
-      </c>
-      <c r="F84">
-        <v>3</v>
-      </c>
-      <c r="G84" t="str">
-        <v/>
-      </c>
       <c r="H84" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I84" t="str">
-        <v>N/A</v>
+        <v>3 Full systems replacement</v>
       </c>
       <c r="J84" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K84" t="str">
         <v>Optional</v>
@@ -4542,12 +5380,21 @@
         <v>N/A</v>
       </c>
       <c r="M84" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N84" t="str">
         <v>Optional</v>
       </c>
       <c r="O84" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P84" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q84" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R84" t="str">
         <v/>
       </c>
     </row>
@@ -4562,25 +5409,25 @@
         <v>Process drainage and grease trap</v>
       </c>
       <c r="D85" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E85" t="str">
+        <v>5.3</v>
+      </c>
+      <c r="F85" t="str">
+        <v>Disposal installations</v>
+      </c>
+      <c r="G85" t="str">
         <v>Industrial, Hospitality</v>
       </c>
-      <c r="E85" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F85">
-        <v>3</v>
-      </c>
-      <c r="G85" t="str">
-        <v/>
-      </c>
       <c r="H85" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I85" t="str">
-        <v>N/A</v>
+        <v>3 Full systems replacement</v>
       </c>
       <c r="J85" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K85" t="str">
         <v>Optional</v>
@@ -4589,12 +5436,21 @@
         <v>N/A</v>
       </c>
       <c r="M85" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N85" t="str">
         <v>Optional</v>
       </c>
       <c r="O85" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P85" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q85" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R85" t="str">
         <v/>
       </c>
     </row>
@@ -4609,25 +5465,25 @@
         <v>Industrial process ventilation and LEV</v>
       </c>
       <c r="D86" t="str">
+        <v>Lump sum</v>
+      </c>
+      <c r="E86" t="str">
+        <v>5.7</v>
+      </c>
+      <c r="F86" t="str">
+        <v>Ventilation</v>
+      </c>
+      <c r="G86" t="str">
         <v>Industrial, Education</v>
       </c>
-      <c r="E86" t="str">
-        <v>per_item</v>
-      </c>
-      <c r="F86">
-        <v>3</v>
-      </c>
-      <c r="G86" t="str">
-        <v/>
-      </c>
       <c r="H86" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I86" t="str">
-        <v>N/A</v>
+        <v>3 Full systems replacement</v>
       </c>
       <c r="J86" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K86" t="str">
         <v>Optional</v>
@@ -4636,12 +5492,21 @@
         <v>N/A</v>
       </c>
       <c r="M86" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N86" t="str">
         <v>Optional</v>
       </c>
       <c r="O86" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P86" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q86" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R86" t="str">
         <v/>
       </c>
     </row>
@@ -4656,25 +5521,25 @@
         <v>Standby generator and ATS</v>
       </c>
       <c r="D87" t="str">
+        <v>Lump sum</v>
+      </c>
+      <c r="E87" t="str">
+        <v>5.8</v>
+      </c>
+      <c r="F87" t="str">
+        <v>Electrical installations</v>
+      </c>
+      <c r="G87" t="str">
         <v>Non-Residential</v>
       </c>
-      <c r="E87" t="str">
-        <v>per_item</v>
-      </c>
-      <c r="F87">
-        <v>3</v>
-      </c>
-      <c r="G87" t="str">
-        <v/>
-      </c>
       <c r="H87" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I87" t="str">
-        <v>N/A</v>
+        <v>3 Full systems replacement</v>
       </c>
       <c r="J87" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K87" t="str">
         <v>Optional</v>
@@ -4683,12 +5548,21 @@
         <v>N/A</v>
       </c>
       <c r="M87" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N87" t="str">
         <v>Optional</v>
       </c>
       <c r="O87" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P87" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q87" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R87" t="str">
         <v/>
       </c>
     </row>
@@ -4703,25 +5577,25 @@
         <v>UPS — uninterruptible power supply</v>
       </c>
       <c r="D88" t="str">
+        <v>Lump sum</v>
+      </c>
+      <c r="E88" t="str">
+        <v>5.8</v>
+      </c>
+      <c r="F88" t="str">
+        <v>Electrical installations</v>
+      </c>
+      <c r="G88" t="str">
         <v>Non-Residential</v>
       </c>
-      <c r="E88" t="str">
-        <v>per_item</v>
-      </c>
-      <c r="F88">
-        <v>3</v>
-      </c>
-      <c r="G88" t="str">
-        <v/>
-      </c>
       <c r="H88" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I88" t="str">
-        <v>N/A</v>
+        <v>3 Full systems replacement</v>
       </c>
       <c r="J88" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K88" t="str">
         <v>Optional</v>
@@ -4730,12 +5604,21 @@
         <v>N/A</v>
       </c>
       <c r="M88" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N88" t="str">
         <v>Optional</v>
       </c>
       <c r="O88" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P88" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q88" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R88" t="str">
         <v/>
       </c>
     </row>
@@ -4750,25 +5633,25 @@
         <v>Nurse call system</v>
       </c>
       <c r="D89" t="str">
+        <v>Per unit</v>
+      </c>
+      <c r="E89" t="str">
+        <v>5.12</v>
+      </c>
+      <c r="F89" t="str">
+        <v>Communication, security and control systems</v>
+      </c>
+      <c r="G89" t="str">
         <v>Healthcare</v>
       </c>
-      <c r="E89" t="str">
-        <v>per_nr</v>
-      </c>
-      <c r="F89">
-        <v>3</v>
-      </c>
-      <c r="G89" t="str">
-        <v/>
-      </c>
       <c r="H89" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I89" t="str">
-        <v>N/A</v>
+        <v>3 Full systems replacement</v>
       </c>
       <c r="J89" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K89" t="str">
         <v>Optional</v>
@@ -4777,12 +5660,21 @@
         <v>N/A</v>
       </c>
       <c r="M89" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N89" t="str">
         <v>Optional</v>
       </c>
       <c r="O89" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P89" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q89" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R89" t="str">
         <v/>
       </c>
     </row>
@@ -4797,25 +5689,25 @@
         <v>Precision cooling — CRAC and CRAH</v>
       </c>
       <c r="D90" t="str">
+        <v>Lump sum</v>
+      </c>
+      <c r="E90" t="str">
+        <v>5.6</v>
+      </c>
+      <c r="F90" t="str">
+        <v>Space heating and air conditioning</v>
+      </c>
+      <c r="G90" t="str">
         <v>Industrial</v>
       </c>
-      <c r="E90" t="str">
-        <v>per_item</v>
-      </c>
-      <c r="F90">
-        <v>3</v>
-      </c>
-      <c r="G90" t="str">
-        <v/>
-      </c>
       <c r="H90" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I90" t="str">
-        <v>N/A</v>
+        <v>3 Full systems replacement</v>
       </c>
       <c r="J90" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K90" t="str">
         <v>Optional</v>
@@ -4824,12 +5716,21 @@
         <v>N/A</v>
       </c>
       <c r="M90" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N90" t="str">
         <v>Optional</v>
       </c>
       <c r="O90" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P90" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q90" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R90" t="str">
         <v/>
       </c>
     </row>
@@ -4844,39 +5745,48 @@
         <v>Hand dryers — recessed/surface commercial (per unit)</v>
       </c>
       <c r="D91" t="str">
+        <v>Per unit</v>
+      </c>
+      <c r="E91" t="str">
+        <v>5.1</v>
+      </c>
+      <c r="F91" t="str">
+        <v>Sanitary installations</v>
+      </c>
+      <c r="G91" t="str">
         <v>Non-Residential</v>
       </c>
-      <c r="E91" t="str">
-        <v>per_nr</v>
-      </c>
-      <c r="F91">
-        <v>2</v>
-      </c>
-      <c r="G91" t="str">
-        <v/>
-      </c>
       <c r="H91" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I91" t="str">
-        <v>Optional</v>
+        <v>2 Finishes with minor services</v>
       </c>
       <c r="J91" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K91" t="str">
         <v>Optional</v>
       </c>
       <c r="L91" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M91" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N91" t="str">
         <v>Optional</v>
       </c>
       <c r="O91" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P91" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q91" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R91" t="str">
         <v/>
       </c>
     </row>
@@ -4891,39 +5801,48 @@
         <v>Prefabricated / modular units</v>
       </c>
       <c r="D92" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E92" t="str">
+        <v>6.1</v>
+      </c>
+      <c r="F92" t="str">
+        <v>Prefabricated buildings and building units</v>
+      </c>
+      <c r="G92" t="str">
         <v>All</v>
       </c>
-      <c r="E92" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F92">
-        <v>1</v>
-      </c>
-      <c r="G92" t="str">
-        <v/>
-      </c>
       <c r="H92" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I92" t="str">
-        <v>Optional</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J92" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="K92" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="L92" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M92" t="str">
         <v>N/A</v>
       </c>
       <c r="N92" t="str">
-        <v>Optional</v>
+        <v>N/A</v>
       </c>
       <c r="O92" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P92" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q92" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R92" t="str">
         <v/>
       </c>
     </row>
@@ -4938,39 +5857,48 @@
         <v>Pre-engineered systems (mezzanine)</v>
       </c>
       <c r="D93" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E93" t="str">
+        <v>6.1</v>
+      </c>
+      <c r="F93" t="str">
+        <v>Prefabricated buildings and building units</v>
+      </c>
+      <c r="G93" t="str">
         <v>Industrial, Retail, Office</v>
       </c>
-      <c r="E93" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F93">
-        <v>1</v>
-      </c>
-      <c r="G93" t="str">
-        <v/>
-      </c>
       <c r="H93" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I93" t="str">
-        <v>Optional</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J93" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="K93" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="L93" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M93" t="str">
         <v>N/A</v>
       </c>
       <c r="N93" t="str">
-        <v>Optional</v>
+        <v>N/A</v>
       </c>
       <c r="O93" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P93" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q93" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R93" t="str">
         <v/>
       </c>
     </row>
@@ -4985,28 +5913,28 @@
         <v>Modular bathroom and WC pod</v>
       </c>
       <c r="D94" t="str">
+        <v>Per unit</v>
+      </c>
+      <c r="E94" t="str">
+        <v>6.1</v>
+      </c>
+      <c r="F94" t="str">
+        <v>Prefabricated buildings and building units</v>
+      </c>
+      <c r="G94" t="str">
         <v>Residential, Healthcare</v>
       </c>
-      <c r="E94" t="str">
-        <v>per_nr</v>
-      </c>
-      <c r="F94">
-        <v>4</v>
-      </c>
-      <c r="G94" t="str">
-        <v/>
-      </c>
       <c r="H94" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I94" t="str">
-        <v>N/A</v>
+        <v>4 Reconfiguration or full redesign</v>
       </c>
       <c r="J94" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="K94" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="L94" t="str">
         <v>N/A</v>
@@ -5015,9 +5943,18 @@
         <v>N/A</v>
       </c>
       <c r="N94" t="str">
-        <v>Optional</v>
+        <v>N/A</v>
       </c>
       <c r="O94" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P94" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q94" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R94" t="str">
         <v/>
       </c>
     </row>
@@ -5032,28 +5969,28 @@
         <v>Cleanroom structure</v>
       </c>
       <c r="D95" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E95" t="str">
+        <v>6.1</v>
+      </c>
+      <c r="F95" t="str">
+        <v>Prefabricated buildings and building units</v>
+      </c>
+      <c r="G95" t="str">
         <v>Healthcare, Education, Industrial</v>
       </c>
-      <c r="E95" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F95">
-        <v>4</v>
-      </c>
-      <c r="G95" t="str">
-        <v/>
-      </c>
       <c r="H95" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I95" t="str">
-        <v>N/A</v>
+        <v>4 Reconfiguration or full redesign</v>
       </c>
       <c r="J95" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="K95" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="L95" t="str">
         <v>N/A</v>
@@ -5062,9 +5999,18 @@
         <v>N/A</v>
       </c>
       <c r="N95" t="str">
-        <v>Optional</v>
+        <v>N/A</v>
       </c>
       <c r="O95" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P95" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q95" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R95" t="str">
         <v/>
       </c>
     </row>
@@ -5079,39 +6025,48 @@
         <v>Structural repairs</v>
       </c>
       <c r="D96" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E96" t="str">
+        <v>7.6</v>
+      </c>
+      <c r="F96" t="str">
+        <v>Renovation works</v>
+      </c>
+      <c r="G96" t="str">
         <v>All</v>
       </c>
-      <c r="E96" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F96">
-        <v>1</v>
-      </c>
-      <c r="G96" t="str">
-        <v/>
-      </c>
       <c r="H96" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="I96" t="str">
-        <v>Optional</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J96" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K96" t="str">
         <v>N/A</v>
       </c>
       <c r="L96" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M96" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N96" t="str">
-        <v>Optional</v>
+        <v>N/A</v>
       </c>
       <c r="O96" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P96" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q96" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R96" t="str">
         <v/>
       </c>
     </row>
@@ -5126,39 +6081,48 @@
         <v>Fabric / envelope repairs</v>
       </c>
       <c r="D97" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E97" t="str">
+        <v>7.6</v>
+      </c>
+      <c r="F97" t="str">
+        <v>Renovation works</v>
+      </c>
+      <c r="G97" t="str">
         <v>All</v>
       </c>
-      <c r="E97" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F97">
-        <v>1</v>
-      </c>
-      <c r="G97" t="str">
-        <v/>
-      </c>
       <c r="H97" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="I97" t="str">
-        <v>Optional</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J97" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K97" t="str">
         <v>N/A</v>
       </c>
       <c r="L97" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M97" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N97" t="str">
-        <v>Optional</v>
+        <v>N/A</v>
       </c>
       <c r="O97" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P97" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q97" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R97" t="str">
         <v/>
       </c>
     </row>
@@ -5173,39 +6137,48 @@
         <v>Damp proof course treatment</v>
       </c>
       <c r="D98" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E98" t="str">
+        <v>7.3</v>
+      </c>
+      <c r="F98" t="str">
+        <v>Damp-proof courses/fungus and beetle eradication</v>
+      </c>
+      <c r="G98" t="str">
         <v>All</v>
       </c>
-      <c r="E98" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F98">
-        <v>1</v>
-      </c>
-      <c r="G98" t="str">
-        <v/>
-      </c>
       <c r="H98" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="I98" t="str">
-        <v>Optional</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J98" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K98" t="str">
         <v>N/A</v>
       </c>
       <c r="L98" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M98" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N98" t="str">
-        <v>Optional</v>
+        <v>N/A</v>
       </c>
       <c r="O98" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P98" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q98" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R98" t="str">
         <v/>
       </c>
     </row>
@@ -5220,39 +6193,48 @@
         <v>M&amp;E overhaul / life-expired services</v>
       </c>
       <c r="D99" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E99" t="str">
+        <v>7.2</v>
+      </c>
+      <c r="F99" t="str">
+        <v>Repairs to existing services</v>
+      </c>
+      <c r="G99" t="str">
         <v>All</v>
       </c>
-      <c r="E99" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F99">
-        <v>1</v>
-      </c>
-      <c r="G99" t="str">
-        <v/>
-      </c>
       <c r="H99" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="I99" t="str">
-        <v>Optional</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J99" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K99" t="str">
         <v>N/A</v>
       </c>
       <c r="L99" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M99" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N99" t="str">
-        <v>Optional</v>
+        <v>N/A</v>
       </c>
       <c r="O99" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P99" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q99" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R99" t="str">
         <v/>
       </c>
     </row>
@@ -5267,39 +6249,48 @@
         <v>Making good after structural works</v>
       </c>
       <c r="D100" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E100" t="str">
+        <v>7.1</v>
+      </c>
+      <c r="F100" t="str">
+        <v>Minor demolition works and alterations</v>
+      </c>
+      <c r="G100" t="str">
         <v>All</v>
       </c>
-      <c r="E100" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F100">
-        <v>1</v>
-      </c>
-      <c r="G100" t="str">
-        <v/>
-      </c>
       <c r="H100" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="I100" t="str">
-        <v>Optional</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J100" t="str">
+        <v/>
+      </c>
+      <c r="K100" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="L100" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="M100" t="str">
         <v>Core</v>
       </c>
-      <c r="K100" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="L100" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="M100" t="str">
-        <v>N/A</v>
-      </c>
       <c r="N100" t="str">
-        <v>Optional</v>
+        <v>N/A</v>
       </c>
       <c r="O100" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P100" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q100" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R100" t="str">
         <v/>
       </c>
     </row>
@@ -5314,39 +6305,48 @@
         <v>Site preparation &amp; clearance</v>
       </c>
       <c r="D101" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E101" t="str">
+        <v>8.1</v>
+      </c>
+      <c r="F101" t="str">
+        <v>Site preparation works</v>
+      </c>
+      <c r="G101" t="str">
         <v>All</v>
       </c>
-      <c r="E101" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F101">
-        <v>1</v>
-      </c>
-      <c r="G101" t="str">
-        <v/>
-      </c>
       <c r="H101" t="str">
+        <v/>
+      </c>
+      <c r="I101" t="str">
+        <v>1 Fabric and finishes only</v>
+      </c>
+      <c r="J101" t="str">
+        <v/>
+      </c>
+      <c r="K101" t="str">
         <v>Core</v>
-      </c>
-      <c r="I101" t="str">
-        <v>Core</v>
-      </c>
-      <c r="J101" t="str">
-        <v>Optional</v>
-      </c>
-      <c r="K101" t="str">
-        <v>N/A</v>
       </c>
       <c r="L101" t="str">
         <v>Core</v>
       </c>
       <c r="M101" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N101" t="str">
-        <v>Optional</v>
+        <v>N/A</v>
       </c>
       <c r="O101" t="str">
+        <v>Core</v>
+      </c>
+      <c r="P101" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q101" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R101" t="str">
         <v/>
       </c>
     </row>
@@ -5361,39 +6361,48 @@
         <v>Roads, paths &amp; hard paving</v>
       </c>
       <c r="D102" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E102" t="str">
+        <v>8.2</v>
+      </c>
+      <c r="F102" t="str">
+        <v>Roads, paths, pavings and surfacings</v>
+      </c>
+      <c r="G102" t="str">
         <v>All</v>
       </c>
-      <c r="E102" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F102">
-        <v>1</v>
-      </c>
-      <c r="G102" t="str">
-        <v/>
-      </c>
       <c r="H102" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I102" t="str">
-        <v>Optional</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J102" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="L102" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="M102" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="N102" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="O102" t="str">
         <v>Core</v>
       </c>
-      <c r="M102" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="N102" t="str">
-        <v>Optional</v>
-      </c>
-      <c r="O102" t="str">
+      <c r="P102" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q102" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R102" t="str">
         <v/>
       </c>
     </row>
@@ -5408,39 +6417,48 @@
         <v>Car parking (line-marked bays)</v>
       </c>
       <c r="D103" t="str">
+        <v>Per unit</v>
+      </c>
+      <c r="E103" t="str">
+        <v>8.2</v>
+      </c>
+      <c r="F103" t="str">
+        <v>Roads, paths, pavings and surfacings</v>
+      </c>
+      <c r="G103" t="str">
         <v>All</v>
       </c>
-      <c r="E103" t="str">
-        <v>per_nr</v>
-      </c>
-      <c r="F103">
-        <v>1</v>
-      </c>
-      <c r="G103" t="str">
-        <v/>
-      </c>
       <c r="H103" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I103" t="str">
-        <v>Optional</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J103" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K103" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="L103" t="str">
         <v>Optional</v>
       </c>
       <c r="M103" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N103" t="str">
-        <v>Optional</v>
+        <v>N/A</v>
       </c>
       <c r="O103" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="P103" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q103" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R103" t="str">
         <v/>
       </c>
     </row>
@@ -5455,39 +6473,48 @@
         <v>Surface water drainage</v>
       </c>
       <c r="D104" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E104" t="str">
+        <v>8.6</v>
+      </c>
+      <c r="F104" t="str">
+        <v>External drainage</v>
+      </c>
+      <c r="G104" t="str">
         <v>All</v>
       </c>
-      <c r="E104" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F104">
-        <v>1</v>
-      </c>
-      <c r="G104" t="str">
-        <v/>
-      </c>
       <c r="H104" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I104" t="str">
-        <v>Optional</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J104" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K104" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="L104" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="M104" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="N104" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="O104" t="str">
         <v>Core</v>
       </c>
-      <c r="M104" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="N104" t="str">
-        <v>Optional</v>
-      </c>
-      <c r="O104" t="str">
+      <c r="P104" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q104" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R104" t="str">
         <v/>
       </c>
     </row>
@@ -5502,39 +6529,48 @@
         <v>Foul drainage connections</v>
       </c>
       <c r="D105" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E105" t="str">
+        <v>8.6</v>
+      </c>
+      <c r="F105" t="str">
+        <v>External drainage</v>
+      </c>
+      <c r="G105" t="str">
         <v>All</v>
       </c>
-      <c r="E105" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F105">
-        <v>1</v>
-      </c>
-      <c r="G105" t="str">
-        <v/>
-      </c>
       <c r="H105" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I105" t="str">
-        <v>Optional</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J105" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K105" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="L105" t="str">
         <v>Optional</v>
       </c>
       <c r="M105" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N105" t="str">
-        <v>Optional</v>
+        <v>N/A</v>
       </c>
       <c r="O105" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="P105" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q105" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R105" t="str">
         <v/>
       </c>
     </row>
@@ -5549,39 +6585,48 @@
         <v>External utility services</v>
       </c>
       <c r="D106" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E106" t="str">
+        <v>8.7</v>
+      </c>
+      <c r="F106" t="str">
+        <v>External services</v>
+      </c>
+      <c r="G106" t="str">
         <v>All</v>
       </c>
-      <c r="E106" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F106">
-        <v>1</v>
-      </c>
-      <c r="G106" t="str">
-        <v/>
-      </c>
       <c r="H106" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I106" t="str">
-        <v>Optional</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J106" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K106" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="L106" t="str">
         <v>Optional</v>
       </c>
       <c r="M106" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N106" t="str">
-        <v>Optional</v>
+        <v>N/A</v>
       </c>
       <c r="O106" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="P106" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q106" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R106" t="str">
         <v/>
       </c>
     </row>
@@ -5596,39 +6641,48 @@
         <v>Soft landscaping</v>
       </c>
       <c r="D107" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E107" t="str">
+        <v>8.3</v>
+      </c>
+      <c r="F107" t="str">
+        <v>Soft landscaping, planting and irrigation systems</v>
+      </c>
+      <c r="G107" t="str">
         <v>All</v>
       </c>
-      <c r="E107" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F107">
-        <v>1</v>
-      </c>
-      <c r="G107" t="str">
-        <v/>
-      </c>
       <c r="H107" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I107" t="str">
-        <v>Optional</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J107" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K107" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="L107" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="M107" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="N107" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="O107" t="str">
         <v>Core</v>
       </c>
-      <c r="M107" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="N107" t="str">
-        <v>Optional</v>
-      </c>
-      <c r="O107" t="str">
+      <c r="P107" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q107" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R107" t="str">
         <v/>
       </c>
     </row>
@@ -5643,39 +6697,48 @@
         <v>Boundary enclosures (fences/gates)</v>
       </c>
       <c r="D108" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E108" t="str">
+        <v>8.4</v>
+      </c>
+      <c r="F108" t="str">
+        <v>Fencing, railings and walls</v>
+      </c>
+      <c r="G108" t="str">
         <v>All</v>
       </c>
-      <c r="E108" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F108">
-        <v>1</v>
-      </c>
-      <c r="G108" t="str">
-        <v/>
-      </c>
       <c r="H108" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I108" t="str">
-        <v>Optional</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J108" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K108" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="L108" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="M108" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="N108" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="O108" t="str">
         <v>Core</v>
       </c>
-      <c r="M108" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="N108" t="str">
-        <v>Optional</v>
-      </c>
-      <c r="O108" t="str">
+      <c r="P108" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q108" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R108" t="str">
         <v/>
       </c>
     </row>
@@ -5690,39 +6753,48 @@
         <v>External lighting (site-wide)</v>
       </c>
       <c r="D109" t="str">
+        <v>Per unit</v>
+      </c>
+      <c r="E109" t="str">
+        <v>8.7</v>
+      </c>
+      <c r="F109" t="str">
+        <v>External services</v>
+      </c>
+      <c r="G109" t="str">
         <v>All</v>
       </c>
-      <c r="E109" t="str">
-        <v>per_nr</v>
-      </c>
-      <c r="F109">
-        <v>1</v>
-      </c>
-      <c r="G109" t="str">
-        <v/>
-      </c>
       <c r="H109" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I109" t="str">
-        <v>Optional</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J109" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K109" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="L109" t="str">
         <v>Optional</v>
       </c>
       <c r="M109" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N109" t="str">
-        <v>Optional</v>
+        <v>N/A</v>
       </c>
       <c r="O109" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="P109" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q109" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R109" t="str">
         <v/>
       </c>
     </row>
@@ -5737,28 +6809,28 @@
         <v>HGV hardstanding and turning area</v>
       </c>
       <c r="D110" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E110" t="str">
+        <v>8.2</v>
+      </c>
+      <c r="F110" t="str">
+        <v>Roads, paths, pavings and surfacings</v>
+      </c>
+      <c r="G110" t="str">
         <v>Industrial</v>
       </c>
-      <c r="E110" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F110">
-        <v>1</v>
-      </c>
-      <c r="G110" t="str">
-        <v/>
-      </c>
       <c r="H110" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I110" t="str">
-        <v>Optional</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J110" t="str">
-        <v>N/A</v>
+        <v/>
       </c>
       <c r="K110" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="L110" t="str">
         <v>Optional</v>
@@ -5767,9 +6839,18 @@
         <v>N/A</v>
       </c>
       <c r="N110" t="str">
-        <v>Optional</v>
+        <v>N/A</v>
       </c>
       <c r="O110" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="P110" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q110" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R110" t="str">
         <v/>
       </c>
     </row>
@@ -5784,39 +6865,48 @@
         <v>Cycle storage and shelters</v>
       </c>
       <c r="D111" t="str">
+        <v>Per unit</v>
+      </c>
+      <c r="E111" t="str">
+        <v>8.8</v>
+      </c>
+      <c r="F111" t="str">
+        <v>Minor building works and ancillary buildings</v>
+      </c>
+      <c r="G111" t="str">
         <v>All</v>
       </c>
-      <c r="E111" t="str">
-        <v>per_nr</v>
-      </c>
-      <c r="F111">
-        <v>1</v>
-      </c>
-      <c r="G111" t="str">
-        <v/>
-      </c>
       <c r="H111" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I111" t="str">
-        <v>Optional</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J111" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K111" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="L111" t="str">
         <v>Optional</v>
       </c>
       <c r="M111" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N111" t="str">
-        <v>Optional</v>
+        <v>N/A</v>
       </c>
       <c r="O111" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="P111" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q111" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R111" t="str">
         <v/>
       </c>
     </row>
@@ -5831,39 +6921,48 @@
         <v>Bin store and waste management enclosure</v>
       </c>
       <c r="D112" t="str">
+        <v>Lump sum</v>
+      </c>
+      <c r="E112" t="str">
+        <v>8.8</v>
+      </c>
+      <c r="F112" t="str">
+        <v>Minor building works and ancillary buildings</v>
+      </c>
+      <c r="G112" t="str">
         <v>All</v>
       </c>
-      <c r="E112" t="str">
-        <v>per_item</v>
-      </c>
-      <c r="F112">
-        <v>1</v>
-      </c>
-      <c r="G112" t="str">
-        <v/>
-      </c>
       <c r="H112" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I112" t="str">
-        <v>Optional</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J112" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K112" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="L112" t="str">
         <v>Optional</v>
       </c>
       <c r="M112" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N112" t="str">
-        <v>Optional</v>
+        <v>N/A</v>
       </c>
       <c r="O112" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="P112" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q112" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R112" t="str">
         <v/>
       </c>
     </row>
@@ -5878,45 +6977,54 @@
         <v>Roof terrace and green roof</v>
       </c>
       <c r="D113" t="str">
+        <v>Every floor (GIFA)</v>
+      </c>
+      <c r="E113" t="str">
+        <v>2.3</v>
+      </c>
+      <c r="F113" t="str">
+        <v>Roof</v>
+      </c>
+      <c r="G113" t="str">
         <v>All</v>
       </c>
-      <c r="E113" t="str">
-        <v>gifa_rate</v>
-      </c>
-      <c r="F113">
-        <v>1</v>
-      </c>
-      <c r="G113" t="str">
-        <v/>
-      </c>
       <c r="H113" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="I113" t="str">
-        <v>Optional</v>
+        <v>1 Fabric and finishes only</v>
       </c>
       <c r="J113" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="K113" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="L113" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="M113" t="str">
-        <v>N/A</v>
+        <v>Optional</v>
       </c>
       <c r="N113" t="str">
-        <v>Optional</v>
+        <v>N/A</v>
       </c>
       <c r="O113" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="P113" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Q113" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="R113" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O113"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R113"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -6197,12 +7305,33 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>If your sheet marks these Core, the default view becomes:</v>
+        <v>Core once this sheet is applied — how many tiles the user sees first:</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>(fill sheet 1, re-run this script, and this row fills in)</v>
+        <v>Any (wildcard)</v>
+      </c>
+      <c r="B13">
+        <v>19</v>
+      </c>
+      <c r="C13">
+        <v>19</v>
+      </c>
+      <c r="D13">
+        <v>14</v>
+      </c>
+      <c r="E13">
+        <v>9</v>
+      </c>
+      <c r="F13">
+        <v>5</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6553,4 +7682,124 @@
     <ignoredError numberStoredAsText="1" sqref="A1:J10"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C11"/>
+  <cols>
+    <col min="1" max="1" width="34.83203125" customWidth="1"/>
+    <col min="2" max="2" width="42.83203125" customWidth="1"/>
+    <col min="3" max="3" width="90.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Level of works (Q2.2)</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Elements available at this level and below</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Applies to</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1 Fabric and finishes only</v>
+      </c>
+      <c r="B2">
+        <v>49</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Refurbishment, Fit-out, Extension only</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2 Finishes with minor services</v>
+      </c>
+      <c r="B3">
+        <v>66</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Refurbishment, Fit-out, Extension only</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>3 Full systems replacement</v>
+      </c>
+      <c r="B4">
+        <v>96</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Refurbishment, Fit-out, Extension only</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>4 Reconfiguration or full redesign</v>
+      </c>
+      <c r="B5">
+        <v>109</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Refurbishment, Fit-out, Extension only</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Elements that first become available at each level:</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1 Fabric and finishes only</v>
+      </c>
+      <c r="B8">
+        <v>49</v>
+      </c>
+      <c r="C8" t="str">
+        <v>0.1, 0.5, 1.2, 1.4, 2.3, 2.5, 2.6, 2.8, 2.9, 3.1, 3.2, 3.3, 4.1, 4.5, 4.6, 4.7, 4.8, 4.9, 4.12, 4.13, 4.15, 4.19, 4.20, 4.24, 4.25, 4.28, 4.30, 5.1b, 5.10, 6.1, 6.2, 7.1, 7.2, 7.3, 7.4, 7.5, 8.1, 8.2, 8.3, 8.4, 8.5, 8.6, 8.7, 8.8, 8.9, 8.10, 8.11, 8.12, 8.13</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>2 Finishes with minor services</v>
+      </c>
+      <c r="B9">
+        <v>17</v>
+      </c>
+      <c r="C9" t="str">
+        <v>2.4, 4.2-COM, 4.2-HC, 4.2-HG, 4.2-HP, 4.2-RES, 4.3, 4.22, 4.26, 4.27, 4.31-NR, 4.32-HOH, 5.1, 5.8b, 5.8c, 5.16, 5.30-NR</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>3 Full systems replacement</v>
+      </c>
+      <c r="B10">
+        <v>30</v>
+      </c>
+      <c r="C10" t="str">
+        <v>4.4, 4.10, 4.11, 4.16, 4.18, 4.21, 5.2, 5.3, 5.4, 5.6, 5.7, 5.7a, 5.8a, 5.9a, 5.9b, 5.11, 5.12, 5.13, 5.14, 5.15, 5.18, 5.19, 5.20, 5.21, 5.23, 5.24, 5.25, 5.26, 5.27, 5.29</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>4 Reconfiguration or full redesign</v>
+      </c>
+      <c r="B11">
+        <v>13</v>
+      </c>
+      <c r="C11" t="str">
+        <v>0.2, 0.3, 0.4, 1.1, 1.3, 2.1, 2.2, 2.7, 4.14, 4.17, 4.29, 6.3, 6.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
+  </ignoredErrors>
+</worksheet>
 </file>